--- a/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_43.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_43.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2786307.359561127</v>
+        <v>2779390.788954095</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9947345.838828404</v>
+        <v>9956801.353979923</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9947345.838828404</v>
+        <v>9956801.353979923</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14825318.0370755</v>
+        <v>14825228.78987928</v>
       </c>
     </row>
   </sheetData>
@@ -663,7 +663,7 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E2" t="n">
-        <v>4.363289606868648</v>
+        <v>172.7782809922831</v>
       </c>
       <c r="F2" t="n">
         <v>4.889628708011855</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>168.4149913854146</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>94.84816780232291</v>
@@ -739,22 +739,22 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>192.3498461705184</v>
       </c>
       <c r="E3" t="n">
-        <v>292.6615515943715</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -897,13 +897,13 @@
         <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
-        <v>10.33915573984979</v>
+        <v>178.7541471252643</v>
       </c>
       <c r="E5" t="n">
         <v>4.363289606868648</v>
       </c>
       <c r="F5" t="n">
-        <v>173.3046200934263</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
         <v>3.75737228701621</v>
@@ -970,13 +970,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1015,16 +1015,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
-        <v>272.5051781317728</v>
+        <v>421</v>
       </c>
       <c r="S6" t="n">
-        <v>66.5639999646113</v>
+        <v>421</v>
       </c>
       <c r="T6" t="n">
-        <v>5.357765217513816</v>
+        <v>61.84192176744759</v>
       </c>
       <c r="U6" t="n">
         <v>0.2103597601867477</v>
@@ -1137,10 +1137,10 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
-        <v>4.363289606868648</v>
+        <v>22.69712130959848</v>
       </c>
       <c r="F8" t="n">
-        <v>173.3046200934263</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
         <v>3.75737228701621</v>
@@ -1149,7 +1149,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1219,13 +1219,13 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>199.8180013219742</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1261,16 +1261,16 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T9" t="n">
-        <v>405.3577652175138</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
-        <v>400.2103597601867</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>90.09876729325129</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
@@ -1386,7 +1386,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I11" t="n">
-        <v>7.846191385414503</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1462,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>62.67776252544243</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S12" t="n">
-        <v>116.5639999646113</v>
+        <v>466.5639999646113</v>
       </c>
       <c r="T12" t="n">
         <v>55.35776521751382</v>
@@ -1507,10 +1507,10 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>145.0509054352711</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X12" t="n">
-        <v>419.8627394453875</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y12" t="n">
         <v>49.39139276613435</v>
@@ -1623,7 +1623,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I14" t="n">
-        <v>7.846191385414503</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1684,7 +1684,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>361.0999124455193</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -1696,13 +1696,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>62.67776252544269</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1729,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>197.2737972923793</v>
+        <v>284.2120239427945</v>
       </c>
       <c r="S15" t="n">
         <v>116.5639999646113</v>
@@ -1857,10 +1857,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H17" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I17" t="n">
-        <v>7.846191385414503</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>384.5565566463266</v>
+        <v>97.2343191717691</v>
       </c>
       <c r="C18" t="n">
         <v>11.09991244551929</v>
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>62.67776252544266</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1987,7 +1987,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y18" t="n">
-        <v>49.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="19">
@@ -2094,7 +2094,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H20" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>7.846191385414608</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>144.8481678023229</v>
@@ -2164,7 +2164,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>80.50967533902158</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -2173,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>332.1680871864211</v>
+        <v>62.67776252544243</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S21" t="n">
         <v>116.5639999646113</v>
@@ -2331,7 +2331,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H23" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2367,7 +2367,7 @@
         <v>144.8481678023229</v>
       </c>
       <c r="T23" t="n">
-        <v>244.5217731139785</v>
+        <v>236.6755817285639</v>
       </c>
       <c r="U23" t="n">
         <v>299.2212965486107</v>
@@ -2395,7 +2395,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>73.77767497096187</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -2410,7 +2410,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>197.2737972923793</v>
+        <v>277.7834726314007</v>
       </c>
       <c r="S24" t="n">
         <v>116.5639999646113</v>
@@ -2455,7 +2455,7 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>432.3731429098285</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X24" t="n">
         <v>69.86273944538755</v>
@@ -2565,7 +2565,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H26" t="n">
         <v>58.00965870352741</v>
@@ -2619,7 +2619,7 @@
         <v>242.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>169.1636240682209</v>
+        <v>161.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -2632,7 +2632,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>73.77767497096193</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -2677,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>197.2737972923793</v>
+        <v>259.9515598178218</v>
       </c>
       <c r="S27" t="n">
         <v>116.5639999646113</v>
@@ -2698,7 +2698,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y27" t="n">
-        <v>399.3913927661343</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="28">
@@ -2805,10 +2805,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H29" t="n">
-        <v>65.85585008894192</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2875,16 +2875,16 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>80.50967533902147</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>62.67776252544257</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T30" t="n">
-        <v>405.3577652175138</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U30" t="n">
         <v>50.21035976018675</v>
@@ -3030,7 +3030,7 @@
         <v>99.47457824299391</v>
       </c>
       <c r="D32" t="n">
-        <v>68.18534712526427</v>
+        <v>60.33915573984979</v>
       </c>
       <c r="E32" t="n">
         <v>54.36328960686865</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S32" t="n">
         <v>144.8481678023229</v>
@@ -3106,19 +3106,19 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>11.09991244551929</v>
+        <v>75.83998807325922</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>86.93822665041533</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>152.6943591877374</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T35" t="n">
         <v>236.6755817285639</v>
@@ -3340,22 +3340,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C36" t="n">
-        <v>11.09991244551929</v>
+        <v>73.77767497096181</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>86.93822665041533</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>7.846191385414608</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>144.8481678023229</v>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>107.5980768338924</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
-        <v>11.09991244551929</v>
+        <v>73.77767497096181</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -3589,7 +3589,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3756,7 +3756,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>7.846191385414608</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>144.8481678023229</v>
@@ -3862,10 +3862,10 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S42" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900537</v>
       </c>
       <c r="T42" t="n">
         <v>55.35776521751382</v>
@@ -3874,7 +3874,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V42" t="n">
-        <v>127.1884297169627</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W42" t="n">
         <v>82.37314290982852</v>
@@ -3883,7 +3883,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y42" t="n">
-        <v>399.3913927661343</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="43">
@@ -3993,7 +3993,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I44" t="n">
-        <v>7.846191385414503</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S44" t="n">
         <v>144.8481678023229</v>
@@ -4057,7 +4057,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D45" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>197.2737972923793</v>
+        <v>259.9515598178218</v>
       </c>
       <c r="S45" t="n">
         <v>116.5639999646113</v>
@@ -4111,7 +4111,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V45" t="n">
-        <v>129.2507428192602</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W45" t="n">
         <v>82.37314290982852</v>
@@ -4297,13 +4297,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>115.3301851396645</v>
+        <v>285.4463380542246</v>
       </c>
       <c r="C2" t="n">
-        <v>65.35586368209485</v>
+        <v>235.472016596655</v>
       </c>
       <c r="D2" t="n">
-        <v>54.91227202568093</v>
+        <v>225.028424940241</v>
       </c>
       <c r="E2" t="n">
         <v>50.50490878641967</v>
@@ -4321,52 +4321,52 @@
         <v>33.68</v>
       </c>
       <c r="J2" t="n">
-        <v>424.9891130376557</v>
+        <v>33.68</v>
       </c>
       <c r="K2" t="n">
-        <v>424.9891130376557</v>
+        <v>33.68</v>
       </c>
       <c r="L2" t="n">
-        <v>424.9891130376557</v>
+        <v>33.68</v>
       </c>
       <c r="M2" t="n">
-        <v>424.9891130376558</v>
+        <v>433.6300000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>841.7791130376559</v>
+        <v>850.4200000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>1258.569113037656</v>
+        <v>1267.21</v>
       </c>
       <c r="P2" t="n">
-        <v>1267.21</v>
+        <v>1684</v>
       </c>
       <c r="Q2" t="n">
         <v>1684</v>
       </c>
       <c r="R2" t="n">
-        <v>1513.88384708544</v>
+        <v>1684</v>
       </c>
       <c r="S2" t="n">
-        <v>1418.077616982083</v>
+        <v>1588.193769896644</v>
       </c>
       <c r="T2" t="n">
-        <v>1229.516423316867</v>
+        <v>1399.632576231427</v>
       </c>
       <c r="U2" t="n">
-        <v>977.7777399344324</v>
+        <v>1147.893892848992</v>
       </c>
       <c r="V2" t="n">
-        <v>745.6049882507718</v>
+        <v>915.7211411653319</v>
       </c>
       <c r="W2" t="n">
-        <v>504.8236993811278</v>
+        <v>674.9398522956878</v>
       </c>
       <c r="X2" t="n">
-        <v>310.5996251784331</v>
+        <v>480.7157780929932</v>
       </c>
       <c r="Y2" t="n">
-        <v>198.1577739836791</v>
+        <v>368.2739268982392</v>
       </c>
     </row>
     <row r="3">
@@ -4382,19 +4382,19 @@
         <v>900.0695195792149</v>
       </c>
       <c r="D3" t="n">
-        <v>548.6173105916364</v>
+        <v>705.7767456696004</v>
       </c>
       <c r="E3" t="n">
-        <v>252.9995817084329</v>
+        <v>705.7767456696004</v>
       </c>
       <c r="F3" t="n">
-        <v>252.9995817084329</v>
+        <v>362.7098342171994</v>
       </c>
       <c r="G3" t="n">
-        <v>252.9995817084329</v>
+        <v>33.68</v>
       </c>
       <c r="H3" t="n">
-        <v>252.9995817084329</v>
+        <v>33.68</v>
       </c>
       <c r="I3" t="n">
         <v>33.68</v>
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>794.7745014142688</v>
+        <v>1003.915674768119</v>
       </c>
       <c r="C4" t="n">
-        <v>794.7745014142688</v>
+        <v>1129.917680586555</v>
       </c>
       <c r="D4" t="n">
-        <v>794.7745014142688</v>
+        <v>1243.236824711555</v>
       </c>
       <c r="E4" t="n">
-        <v>912.6034056256818</v>
+        <v>1361.065728922968</v>
       </c>
       <c r="F4" t="n">
-        <v>1036.964378217617</v>
+        <v>1485.426701514903</v>
       </c>
       <c r="G4" t="n">
-        <v>1190.370944104503</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="H4" t="n">
-        <v>1212.989930203873</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="I4" t="n">
-        <v>1434.122809139956</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="J4" t="n">
-        <v>1434.122809139956</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="K4" t="n">
         <v>1544.487243076824</v>
@@ -4506,25 +4506,25 @@
         <v>33.68</v>
       </c>
       <c r="S4" t="n">
-        <v>33.68</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="T4" t="n">
-        <v>221.7556791588049</v>
+        <v>259.005934252978</v>
       </c>
       <c r="U4" t="n">
-        <v>221.7556791588049</v>
+        <v>259.005934252978</v>
       </c>
       <c r="V4" t="n">
-        <v>420.5770720447508</v>
+        <v>457.8273271389239</v>
       </c>
       <c r="W4" t="n">
-        <v>420.5770720447508</v>
+        <v>629.7182453986013</v>
       </c>
       <c r="X4" t="n">
-        <v>571.6078630689443</v>
+        <v>780.7490364227948</v>
       </c>
       <c r="Y4" t="n">
-        <v>683.0171637479766</v>
+        <v>892.1583371018271</v>
       </c>
     </row>
     <row r="5">
@@ -4540,10 +4540,10 @@
         <v>235.472016596655</v>
       </c>
       <c r="D5" t="n">
-        <v>225.028424940241</v>
+        <v>54.91227202568093</v>
       </c>
       <c r="E5" t="n">
-        <v>220.6210617009798</v>
+        <v>50.50490878641967</v>
       </c>
       <c r="F5" t="n">
         <v>45.565889889438</v>
@@ -4561,22 +4561,22 @@
         <v>33.68</v>
       </c>
       <c r="K5" t="n">
-        <v>33.68</v>
+        <v>450.47</v>
       </c>
       <c r="L5" t="n">
-        <v>33.68</v>
+        <v>850.4200000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>450.47</v>
+        <v>1267.21</v>
       </c>
       <c r="N5" t="n">
-        <v>867.26</v>
+        <v>1267.21</v>
       </c>
       <c r="O5" t="n">
-        <v>1284.05</v>
+        <v>1267.21</v>
       </c>
       <c r="P5" t="n">
-        <v>1284.05</v>
+        <v>1267.21</v>
       </c>
       <c r="Q5" t="n">
         <v>1684</v>
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>385.1322089875785</v>
+        <v>33.68</v>
       </c>
       <c r="C6" t="n">
-        <v>385.1322089875785</v>
+        <v>33.68</v>
       </c>
       <c r="D6" t="n">
         <v>33.68</v>
@@ -4658,31 +4658,31 @@
         <v>1189.112420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1189.112420368536</v>
+        <v>1014.284879873102</v>
       </c>
       <c r="R6" t="n">
-        <v>913.8546646798762</v>
+        <v>589.0323546205764</v>
       </c>
       <c r="S6" t="n">
-        <v>846.6183010792588</v>
+        <v>163.7798293680511</v>
       </c>
       <c r="T6" t="n">
-        <v>841.206417021164</v>
+        <v>101.3132417241646</v>
       </c>
       <c r="U6" t="n">
-        <v>840.9939324149148</v>
+        <v>101.1007571179154</v>
       </c>
       <c r="V6" t="n">
-        <v>826.3366928275207</v>
+        <v>86.44351753052129</v>
       </c>
       <c r="W6" t="n">
-        <v>793.6365484741585</v>
+        <v>53.74337317715914</v>
       </c>
       <c r="X6" t="n">
-        <v>773.5731752969994</v>
+        <v>33.68</v>
       </c>
       <c r="Y6" t="n">
-        <v>773.5731752969994</v>
+        <v>33.68</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>672.8468823826383</v>
+        <v>1003.915674768119</v>
       </c>
       <c r="C7" t="n">
-        <v>798.8488882010741</v>
+        <v>1129.917680586555</v>
       </c>
       <c r="D7" t="n">
-        <v>912.1680323260742</v>
+        <v>1243.236824711555</v>
       </c>
       <c r="E7" t="n">
-        <v>1029.996936537487</v>
+        <v>1243.236824711555</v>
       </c>
       <c r="F7" t="n">
-        <v>1029.996936537487</v>
+        <v>1243.236824711555</v>
       </c>
       <c r="G7" t="n">
-        <v>1183.403502424373</v>
+        <v>1264.606223980558</v>
       </c>
       <c r="H7" t="n">
-        <v>1183.403502424373</v>
+        <v>1434.122809139956</v>
       </c>
       <c r="I7" t="n">
-        <v>1183.403502424373</v>
+        <v>1434.122809139956</v>
       </c>
       <c r="J7" t="n">
-        <v>1544.487243076824</v>
+        <v>1434.122809139956</v>
       </c>
       <c r="K7" t="n">
         <v>1544.487243076824</v>
@@ -4752,16 +4752,16 @@
         <v>259.005934252978</v>
       </c>
       <c r="V7" t="n">
-        <v>259.005934252978</v>
+        <v>457.8273271389239</v>
       </c>
       <c r="W7" t="n">
-        <v>430.8968525126554</v>
+        <v>629.7182453986013</v>
       </c>
       <c r="X7" t="n">
-        <v>561.437581703606</v>
+        <v>780.7490364227948</v>
       </c>
       <c r="Y7" t="n">
-        <v>672.8468823826383</v>
+        <v>892.1583371018271</v>
       </c>
     </row>
     <row r="8">
@@ -4780,16 +4780,16 @@
         <v>225.028424940241</v>
       </c>
       <c r="E8" t="n">
-        <v>220.6210617009798</v>
+        <v>202.1020397790304</v>
       </c>
       <c r="F8" t="n">
-        <v>45.565889889438</v>
+        <v>197.1630208820488</v>
       </c>
       <c r="G8" t="n">
-        <v>41.77056434699738</v>
+        <v>193.3676953396081</v>
       </c>
       <c r="H8" t="n">
-        <v>33.68</v>
+        <v>185.2771309926108</v>
       </c>
       <c r="I8" t="n">
         <v>33.68</v>
@@ -4798,22 +4798,22 @@
         <v>33.68</v>
       </c>
       <c r="K8" t="n">
-        <v>33.68</v>
+        <v>433.6300000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>33.68</v>
+        <v>433.6300000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>450.47</v>
+        <v>850.4200000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>867.26</v>
+        <v>1267.21</v>
       </c>
       <c r="O8" t="n">
-        <v>1284.05</v>
+        <v>1684</v>
       </c>
       <c r="P8" t="n">
-        <v>1284.05</v>
+        <v>1684</v>
       </c>
       <c r="Q8" t="n">
         <v>1684</v>
@@ -4850,22 +4850,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.68</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="C9" t="n">
-        <v>33.68</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="D9" t="n">
-        <v>33.68</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="E9" t="n">
-        <v>33.68</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="F9" t="n">
-        <v>33.68</v>
+        <v>698.2331546075238</v>
       </c>
       <c r="G9" t="n">
-        <v>33.68</v>
+        <v>369.2033203903244</v>
       </c>
       <c r="H9" t="n">
         <v>33.68</v>
@@ -4904,22 +4904,22 @@
         <v>973.1146453614743</v>
       </c>
       <c r="T9" t="n">
-        <v>563.6623572629755</v>
+        <v>967.7027613033796</v>
       </c>
       <c r="U9" t="n">
-        <v>159.4094686163222</v>
+        <v>967.4902766971303</v>
       </c>
       <c r="V9" t="n">
-        <v>144.7522290289281</v>
+        <v>952.8330371097362</v>
       </c>
       <c r="W9" t="n">
-        <v>53.74337317715914</v>
+        <v>920.1328927563741</v>
       </c>
       <c r="X9" t="n">
-        <v>33.68</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="Y9" t="n">
-        <v>33.68</v>
+        <v>900.0695195792149</v>
       </c>
     </row>
     <row r="10">
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>890.5002699879237</v>
+        <v>752.1604946826228</v>
       </c>
       <c r="C10" t="n">
-        <v>1016.50227580636</v>
+        <v>878.1625005010586</v>
       </c>
       <c r="D10" t="n">
-        <v>1016.50227580636</v>
+        <v>991.4816446260587</v>
       </c>
       <c r="E10" t="n">
-        <v>1134.331180017773</v>
+        <v>1109.310548837472</v>
       </c>
       <c r="F10" t="n">
-        <v>1258.692152609708</v>
+        <v>1109.310548837472</v>
       </c>
       <c r="G10" t="n">
-        <v>1412.098718496593</v>
+        <v>1109.310548837472</v>
       </c>
       <c r="H10" t="n">
-        <v>1412.098718496593</v>
+        <v>1278.827133996869</v>
       </c>
       <c r="I10" t="n">
-        <v>1412.098718496593</v>
+        <v>1499.960012932952</v>
       </c>
       <c r="J10" t="n">
-        <v>1434.122809139956</v>
+        <v>1499.960012932952</v>
       </c>
       <c r="K10" t="n">
         <v>1544.487243076824</v>
@@ -4989,16 +4989,16 @@
         <v>317.4814477324597</v>
       </c>
       <c r="V10" t="n">
-        <v>516.3028406184058</v>
+        <v>317.4814477324597</v>
       </c>
       <c r="W10" t="n">
-        <v>516.3028406184058</v>
+        <v>489.3723659921371</v>
       </c>
       <c r="X10" t="n">
-        <v>667.3336316425992</v>
+        <v>640.4031570163306</v>
       </c>
       <c r="Y10" t="n">
-        <v>778.7429323216315</v>
+        <v>640.4031570163306</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>437.4059340138206</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C11" t="n">
-        <v>336.9265620512004</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D11" t="n">
-        <v>275.977919889736</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E11" t="n">
-        <v>221.0655061454243</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F11" t="n">
-        <v>165.6214367433921</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G11" t="n">
-        <v>111.3210606959009</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H11" t="n">
-        <v>52.72544584385304</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I11" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="J11" t="n">
-        <v>181.7520762183974</v>
+        <v>64.92117127106526</v>
       </c>
       <c r="K11" t="n">
-        <v>181.7520762183974</v>
+        <v>618.3311712710653</v>
       </c>
       <c r="L11" t="n">
-        <v>181.7520762183974</v>
+        <v>618.3311712710653</v>
       </c>
       <c r="M11" t="n">
-        <v>692.6009049473324</v>
+        <v>1129.18</v>
       </c>
       <c r="N11" t="n">
-        <v>1247.000904947332</v>
+        <v>1682.59</v>
       </c>
       <c r="O11" t="n">
-        <v>1801.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P11" t="n">
-        <v>1801.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q11" t="n">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="R11" t="n">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="S11" t="n">
-        <v>2093.688719391593</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T11" t="n">
-        <v>1854.622475221327</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U11" t="n">
-        <v>1552.378741333841</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V11" t="n">
-        <v>1269.70093914513</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W11" t="n">
-        <v>978.4145997704354</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X11" t="n">
-        <v>733.6854750626902</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y11" t="n">
-        <v>570.7385733628857</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="12">
@@ -5087,76 +5087,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>56.01203277325182</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C12" t="n">
-        <v>44.8</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="D12" t="n">
-        <v>44.8</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="E12" t="n">
-        <v>44.8</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="F12" t="n">
-        <v>44.8</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="G12" t="n">
-        <v>44.8</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="H12" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="I12" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="J12" t="n">
-        <v>168.756520175299</v>
+        <v>168.6765201752989</v>
       </c>
       <c r="K12" t="n">
-        <v>357.9493362696824</v>
+        <v>357.8693362696823</v>
       </c>
       <c r="L12" t="n">
-        <v>629.2997978648825</v>
+        <v>629.2197978648824</v>
       </c>
       <c r="M12" t="n">
-        <v>715.3803396077418</v>
+        <v>715.3003396077416</v>
       </c>
       <c r="N12" t="n">
-        <v>848.6606242153101</v>
+        <v>848.58062421531</v>
       </c>
       <c r="O12" t="n">
-        <v>1087.703075899029</v>
+        <v>1087.623075899029</v>
       </c>
       <c r="P12" t="n">
-        <v>1200.232420368536</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>1200.232420368536</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R12" t="n">
-        <v>1000.965958457041</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S12" t="n">
-        <v>883.2245443513734</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T12" t="n">
-        <v>827.3076097882282</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U12" t="n">
-        <v>776.5900746769285</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V12" t="n">
-        <v>711.4277845844838</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W12" t="n">
-        <v>564.9117184882504</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X12" t="n">
-        <v>140.8079412706871</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y12" t="n">
-        <v>90.9176455473191</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>870.1258296400258</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C13" t="n">
-        <v>946.6278354584616</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D13" t="n">
-        <v>1010.446979583462</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E13" t="n">
-        <v>1078.775883794875</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F13" t="n">
-        <v>1153.63685638681</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G13" t="n">
-        <v>1257.543422273696</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H13" t="n">
-        <v>1377.560007433093</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I13" t="n">
-        <v>1549.192886369176</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J13" t="n">
-        <v>1860.776627021628</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K13" t="n">
-        <v>1921.641060958496</v>
+        <v>1921.561060958496</v>
       </c>
       <c r="L13" t="n">
-        <v>1847.35052746579</v>
+        <v>1847.270527465789</v>
       </c>
       <c r="M13" t="n">
-        <v>1674.995364432911</v>
+        <v>1674.915364432911</v>
       </c>
       <c r="N13" t="n">
-        <v>1451.576096481714</v>
+        <v>1451.496096481714</v>
       </c>
       <c r="O13" t="n">
-        <v>1158.196738826143</v>
+        <v>1158.116738826143</v>
       </c>
       <c r="P13" t="n">
-        <v>817.3402768783884</v>
+        <v>817.2602768783884</v>
       </c>
       <c r="Q13" t="n">
-        <v>437.7046542262692</v>
+        <v>437.6246542262692</v>
       </c>
       <c r="R13" t="n">
-        <v>57.29846434631862</v>
+        <v>57.21846434631862</v>
       </c>
       <c r="S13" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="T13" t="n">
-        <v>175.6648964865979</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U13" t="n">
-        <v>372.7160891248845</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V13" t="n">
-        <v>522.0374820108304</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W13" t="n">
-        <v>644.4284002705078</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X13" t="n">
-        <v>745.9591912947013</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y13" t="n">
-        <v>807.8684919737336</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="14">
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>437.4059340138206</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C14" t="n">
-        <v>336.9265620512004</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D14" t="n">
-        <v>275.977919889736</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E14" t="n">
-        <v>221.0655061454243</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F14" t="n">
-        <v>165.6214367433921</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G14" t="n">
-        <v>111.3210606959009</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H14" t="n">
-        <v>52.72544584385304</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I14" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="J14" t="n">
-        <v>44.8</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>599.2</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L14" t="n">
-        <v>599.2</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M14" t="n">
-        <v>1110.048828728935</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N14" t="n">
-        <v>1664.448828728935</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O14" t="n">
-        <v>2218.848828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P14" t="n">
-        <v>2218.848828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q14" t="n">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="R14" t="n">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="S14" t="n">
-        <v>2093.688719391593</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T14" t="n">
-        <v>1854.622475221327</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U14" t="n">
-        <v>1552.378741333841</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V14" t="n">
-        <v>1269.70093914513</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W14" t="n">
-        <v>978.4145997704354</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X14" t="n">
-        <v>733.6854750626902</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y14" t="n">
-        <v>570.7385733628857</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>472.8582575464263</v>
+        <v>384.9618669904511</v>
       </c>
       <c r="C15" t="n">
-        <v>108.1108712378209</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="D15" t="n">
-        <v>108.1108712378209</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="E15" t="n">
-        <v>108.1108712378209</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="F15" t="n">
-        <v>108.1108712378209</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="G15" t="n">
-        <v>108.1108712378209</v>
+        <v>44.72</v>
       </c>
       <c r="H15" t="n">
-        <v>108.1108712378209</v>
+        <v>44.72</v>
       </c>
       <c r="I15" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="J15" t="n">
-        <v>168.756520175299</v>
+        <v>168.6765201752989</v>
       </c>
       <c r="K15" t="n">
-        <v>357.9493362696824</v>
+        <v>357.8693362696823</v>
       </c>
       <c r="L15" t="n">
-        <v>629.2997978648825</v>
+        <v>629.2197978648824</v>
       </c>
       <c r="M15" t="n">
-        <v>715.3803396077418</v>
+        <v>715.3003396077416</v>
       </c>
       <c r="N15" t="n">
-        <v>848.6606242153101</v>
+        <v>848.58062421531</v>
       </c>
       <c r="O15" t="n">
-        <v>1087.703075899029</v>
+        <v>1087.623075899029</v>
       </c>
       <c r="P15" t="n">
-        <v>1200.232420368536</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>1200.232420368536</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R15" t="n">
-        <v>1000.965958457041</v>
+        <v>913.0695679010663</v>
       </c>
       <c r="S15" t="n">
-        <v>883.2245443513734</v>
+        <v>795.3281537953983</v>
       </c>
       <c r="T15" t="n">
-        <v>827.3076097882282</v>
+        <v>739.4112192322531</v>
       </c>
       <c r="U15" t="n">
-        <v>776.5900746769285</v>
+        <v>688.6936841209533</v>
       </c>
       <c r="V15" t="n">
-        <v>711.4277845844838</v>
+        <v>623.5313940285087</v>
       </c>
       <c r="W15" t="n">
-        <v>628.2225897260712</v>
+        <v>540.3261991700961</v>
       </c>
       <c r="X15" t="n">
-        <v>557.6541660438616</v>
+        <v>469.7577754878864</v>
       </c>
       <c r="Y15" t="n">
-        <v>507.7638703204935</v>
+        <v>419.8674797645184</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>870.1258296400258</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C16" t="n">
-        <v>946.6278354584616</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D16" t="n">
-        <v>1010.446979583462</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E16" t="n">
-        <v>1078.775883794875</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F16" t="n">
-        <v>1153.63685638681</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G16" t="n">
-        <v>1257.543422273696</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H16" t="n">
-        <v>1377.560007433093</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I16" t="n">
-        <v>1549.192886369176</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J16" t="n">
-        <v>1860.776627021628</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K16" t="n">
-        <v>1921.641060958496</v>
+        <v>1921.561060958496</v>
       </c>
       <c r="L16" t="n">
-        <v>1847.35052746579</v>
+        <v>1847.270527465789</v>
       </c>
       <c r="M16" t="n">
-        <v>1674.995364432911</v>
+        <v>1674.915364432911</v>
       </c>
       <c r="N16" t="n">
-        <v>1451.576096481714</v>
+        <v>1451.496096481714</v>
       </c>
       <c r="O16" t="n">
-        <v>1158.196738826143</v>
+        <v>1158.116738826143</v>
       </c>
       <c r="P16" t="n">
-        <v>817.3402768783884</v>
+        <v>817.2602768783884</v>
       </c>
       <c r="Q16" t="n">
-        <v>437.7046542262692</v>
+        <v>437.6246542262692</v>
       </c>
       <c r="R16" t="n">
-        <v>57.29846434631862</v>
+        <v>57.21846434631862</v>
       </c>
       <c r="S16" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="T16" t="n">
-        <v>175.6648964865979</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U16" t="n">
-        <v>372.7160891248845</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V16" t="n">
-        <v>522.0374820108304</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W16" t="n">
-        <v>644.4284002705078</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X16" t="n">
-        <v>745.9591912947013</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y16" t="n">
-        <v>807.8684919737336</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="17">
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>437.4059340138206</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C17" t="n">
-        <v>336.9265620512004</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D17" t="n">
-        <v>275.977919889736</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E17" t="n">
-        <v>221.0655061454243</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F17" t="n">
-        <v>165.6214367433921</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G17" t="n">
-        <v>111.3210606959009</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H17" t="n">
-        <v>52.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I17" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="J17" t="n">
-        <v>44.8</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>599.2</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L17" t="n">
-        <v>1153.6</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M17" t="n">
-        <v>1247.000904947332</v>
+        <v>1682.59</v>
       </c>
       <c r="N17" t="n">
-        <v>1801.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="O17" t="n">
-        <v>1801.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P17" t="n">
-        <v>1801.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q17" t="n">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="R17" t="n">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="S17" t="n">
-        <v>2093.688719391593</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T17" t="n">
-        <v>1854.622475221327</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U17" t="n">
-        <v>1552.378741333841</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V17" t="n">
-        <v>1269.70093914513</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W17" t="n">
-        <v>978.4145997704354</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X17" t="n">
-        <v>733.6854750626902</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y17" t="n">
-        <v>570.7385733628857</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>119.3229040110727</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C18" t="n">
-        <v>108.1108712378209</v>
+        <v>44.72</v>
       </c>
       <c r="D18" t="n">
-        <v>108.1108712378209</v>
+        <v>44.72</v>
       </c>
       <c r="E18" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="F18" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="G18" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="H18" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="I18" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="J18" t="n">
-        <v>168.756520175299</v>
+        <v>168.6765201752989</v>
       </c>
       <c r="K18" t="n">
-        <v>357.9493362696824</v>
+        <v>357.8693362696823</v>
       </c>
       <c r="L18" t="n">
-        <v>629.2997978648825</v>
+        <v>629.2197978648824</v>
       </c>
       <c r="M18" t="n">
-        <v>715.3803396077418</v>
+        <v>715.3003396077416</v>
       </c>
       <c r="N18" t="n">
-        <v>848.6606242153101</v>
+        <v>848.58062421531</v>
       </c>
       <c r="O18" t="n">
-        <v>1087.703075899029</v>
+        <v>1087.623075899029</v>
       </c>
       <c r="P18" t="n">
-        <v>1200.232420368536</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="Q18" t="n">
-        <v>1200.232420368536</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R18" t="n">
-        <v>1000.965958457041</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S18" t="n">
-        <v>883.2245443513734</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T18" t="n">
-        <v>827.3076097882282</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U18" t="n">
-        <v>776.5900746769285</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V18" t="n">
-        <v>711.4277845844838</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W18" t="n">
-        <v>628.2225897260712</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X18" t="n">
-        <v>557.6541660438616</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y18" t="n">
-        <v>507.7638703204935</v>
+        <v>154.1485167851398</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>870.1258296400258</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C19" t="n">
-        <v>946.6278354584616</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D19" t="n">
-        <v>1010.446979583462</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E19" t="n">
-        <v>1078.775883794875</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F19" t="n">
-        <v>1153.63685638681</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G19" t="n">
-        <v>1257.543422273696</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H19" t="n">
-        <v>1377.560007433093</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I19" t="n">
-        <v>1549.192886369176</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J19" t="n">
-        <v>1860.776627021628</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K19" t="n">
-        <v>1921.641060958496</v>
+        <v>1921.561060958496</v>
       </c>
       <c r="L19" t="n">
-        <v>1847.35052746579</v>
+        <v>1847.270527465789</v>
       </c>
       <c r="M19" t="n">
-        <v>1674.995364432911</v>
+        <v>1674.915364432911</v>
       </c>
       <c r="N19" t="n">
-        <v>1451.576096481714</v>
+        <v>1451.496096481714</v>
       </c>
       <c r="O19" t="n">
-        <v>1158.196738826143</v>
+        <v>1158.116738826143</v>
       </c>
       <c r="P19" t="n">
-        <v>817.3402768783884</v>
+        <v>817.2602768783884</v>
       </c>
       <c r="Q19" t="n">
-        <v>437.7046542262692</v>
+        <v>437.6246542262692</v>
       </c>
       <c r="R19" t="n">
-        <v>57.29846434631862</v>
+        <v>57.21846434631862</v>
       </c>
       <c r="S19" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="T19" t="n">
-        <v>183.3756791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U19" t="n">
-        <v>380.4268717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V19" t="n">
-        <v>522.0374820108304</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W19" t="n">
-        <v>644.4284002705078</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X19" t="n">
-        <v>745.9591912947013</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y19" t="n">
-        <v>807.8684919737336</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="20">
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>429.4804881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C20" t="n">
-        <v>329.0011162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D20" t="n">
-        <v>268.052474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E20" t="n">
-        <v>213.1400603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F20" t="n">
-        <v>157.695990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G20" t="n">
-        <v>103.3956148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H20" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="I20" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="J20" t="n">
-        <v>436.1091130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K20" t="n">
-        <v>436.1091130376557</v>
+        <v>64.9211712710653</v>
       </c>
       <c r="L20" t="n">
-        <v>436.1091130376557</v>
+        <v>64.9211712710653</v>
       </c>
       <c r="M20" t="n">
-        <v>946.9579417665907</v>
+        <v>575.7700000000003</v>
       </c>
       <c r="N20" t="n">
-        <v>1501.357941766591</v>
+        <v>1129.18</v>
       </c>
       <c r="O20" t="n">
-        <v>1501.357941766591</v>
+        <v>1682.59</v>
       </c>
       <c r="P20" t="n">
-        <v>1801.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q20" t="n">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="R20" t="n">
-        <v>2232.074554156147</v>
+        <v>2236</v>
       </c>
       <c r="S20" t="n">
-        <v>2085.76327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T20" t="n">
-        <v>1846.697029377473</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U20" t="n">
-        <v>1544.453295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V20" t="n">
-        <v>1261.775493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W20" t="n">
-        <v>970.4891539265824</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X20" t="n">
-        <v>725.7600292188372</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y20" t="n">
-        <v>562.8131275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>472.8582575464263</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C21" t="n">
-        <v>461.6462247731745</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="D21" t="n">
-        <v>461.6462247731745</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="E21" t="n">
-        <v>380.3233203903244</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="F21" t="n">
-        <v>380.3233203903244</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="G21" t="n">
-        <v>380.3233203903244</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="H21" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="I21" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="J21" t="n">
-        <v>168.756520175299</v>
+        <v>168.6765201752989</v>
       </c>
       <c r="K21" t="n">
-        <v>357.9493362696824</v>
+        <v>357.8693362696823</v>
       </c>
       <c r="L21" t="n">
-        <v>629.2997978648825</v>
+        <v>629.2197978648824</v>
       </c>
       <c r="M21" t="n">
-        <v>715.3803396077418</v>
+        <v>715.3003396077416</v>
       </c>
       <c r="N21" t="n">
-        <v>848.6606242153101</v>
+        <v>848.58062421531</v>
       </c>
       <c r="O21" t="n">
-        <v>1087.703075899029</v>
+        <v>1087.623075899029</v>
       </c>
       <c r="P21" t="n">
-        <v>1200.232420368536</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>1200.232420368536</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R21" t="n">
-        <v>1000.965958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S21" t="n">
-        <v>883.2245443513734</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T21" t="n">
-        <v>827.3076097882282</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U21" t="n">
-        <v>776.5900746769285</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V21" t="n">
-        <v>711.4277845844838</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W21" t="n">
-        <v>628.2225897260712</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X21" t="n">
-        <v>557.6541660438616</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y21" t="n">
-        <v>507.7638703204935</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>870.1258296400258</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C22" t="n">
-        <v>946.6278354584616</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D22" t="n">
-        <v>1010.446979583462</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E22" t="n">
-        <v>1078.775883794875</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F22" t="n">
-        <v>1153.63685638681</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G22" t="n">
-        <v>1257.543422273696</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H22" t="n">
-        <v>1377.560007433093</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I22" t="n">
-        <v>1549.192886369176</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J22" t="n">
-        <v>1860.776627021628</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K22" t="n">
-        <v>1921.641060958496</v>
+        <v>1921.561060958496</v>
       </c>
       <c r="L22" t="n">
-        <v>1847.35052746579</v>
+        <v>1847.270527465789</v>
       </c>
       <c r="M22" t="n">
-        <v>1674.995364432911</v>
+        <v>1674.915364432911</v>
       </c>
       <c r="N22" t="n">
-        <v>1451.576096481714</v>
+        <v>1451.496096481714</v>
       </c>
       <c r="O22" t="n">
-        <v>1158.196738826143</v>
+        <v>1158.116738826143</v>
       </c>
       <c r="P22" t="n">
-        <v>817.3402768783884</v>
+        <v>817.2602768783884</v>
       </c>
       <c r="Q22" t="n">
-        <v>437.7046542262692</v>
+        <v>437.6246542262692</v>
       </c>
       <c r="R22" t="n">
-        <v>57.29846434631862</v>
+        <v>57.21846434631862</v>
       </c>
       <c r="S22" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="T22" t="n">
-        <v>175.6648964865979</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U22" t="n">
-        <v>372.7160891248845</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V22" t="n">
-        <v>522.0374820108304</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W22" t="n">
-        <v>644.4284002705078</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X22" t="n">
-        <v>745.9591912947013</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y22" t="n">
-        <v>807.8684919737336</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="23">
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>429.4804881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C23" t="n">
-        <v>329.0011162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D23" t="n">
-        <v>268.052474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E23" t="n">
-        <v>213.1400603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F23" t="n">
-        <v>157.695990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G23" t="n">
-        <v>103.3956148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H23" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="I23" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="J23" t="n">
-        <v>65.95117127106482</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>65.95117127106482</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L23" t="n">
-        <v>620.3511712710648</v>
+        <v>618.3311712710653</v>
       </c>
       <c r="M23" t="n">
-        <v>1131.2</v>
+        <v>1129.18</v>
       </c>
       <c r="N23" t="n">
-        <v>1685.6</v>
+        <v>1682.59</v>
       </c>
       <c r="O23" t="n">
-        <v>1685.6</v>
+        <v>2236</v>
       </c>
       <c r="P23" t="n">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="Q23" t="n">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="R23" t="n">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="S23" t="n">
-        <v>2093.688719391593</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T23" t="n">
-        <v>1846.697029377473</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U23" t="n">
-        <v>1544.453295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V23" t="n">
-        <v>1261.775493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W23" t="n">
-        <v>970.4891539265824</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X23" t="n">
-        <v>725.7600292188372</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y23" t="n">
-        <v>562.8131275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>119.3229040110726</v>
+        <v>391.4553531635761</v>
       </c>
       <c r="C24" t="n">
-        <v>44.8</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="D24" t="n">
-        <v>44.8</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="E24" t="n">
-        <v>44.8</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="F24" t="n">
-        <v>44.8</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="G24" t="n">
-        <v>44.8</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H24" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="I24" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="J24" t="n">
-        <v>168.756520175299</v>
+        <v>168.6765201752989</v>
       </c>
       <c r="K24" t="n">
-        <v>357.9493362696824</v>
+        <v>357.8693362696823</v>
       </c>
       <c r="L24" t="n">
-        <v>629.2997978648825</v>
+        <v>629.2197978648824</v>
       </c>
       <c r="M24" t="n">
-        <v>715.3803396077418</v>
+        <v>715.3003396077416</v>
       </c>
       <c r="N24" t="n">
-        <v>848.6606242153101</v>
+        <v>848.58062421531</v>
       </c>
       <c r="O24" t="n">
-        <v>1087.703075899029</v>
+        <v>1087.623075899029</v>
       </c>
       <c r="P24" t="n">
-        <v>1200.232420368536</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>1200.232420368536</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R24" t="n">
-        <v>1000.965958457041</v>
+        <v>919.5630540741914</v>
       </c>
       <c r="S24" t="n">
-        <v>883.2245443513734</v>
+        <v>801.8216399685234</v>
       </c>
       <c r="T24" t="n">
-        <v>827.3076097882282</v>
+        <v>745.9047054053782</v>
       </c>
       <c r="U24" t="n">
-        <v>776.5900746769285</v>
+        <v>695.1871702940784</v>
       </c>
       <c r="V24" t="n">
-        <v>711.4277845844838</v>
+        <v>630.0248802016338</v>
       </c>
       <c r="W24" t="n">
-        <v>274.6872361907176</v>
+        <v>546.8196853432211</v>
       </c>
       <c r="X24" t="n">
-        <v>204.1188125085079</v>
+        <v>476.2512616610114</v>
       </c>
       <c r="Y24" t="n">
-        <v>154.2285167851399</v>
+        <v>426.3609659376434</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>877.8366123122328</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C25" t="n">
-        <v>954.3386181306686</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D25" t="n">
-        <v>1018.157762255669</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E25" t="n">
-        <v>1086.486666467082</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F25" t="n">
-        <v>1161.347639059017</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G25" t="n">
-        <v>1257.543422273696</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H25" t="n">
-        <v>1377.560007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I25" t="n">
-        <v>1549.192886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J25" t="n">
-        <v>1860.776627021628</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K25" t="n">
-        <v>1921.641060958496</v>
+        <v>1921.561060958496</v>
       </c>
       <c r="L25" t="n">
-        <v>1847.35052746579</v>
+        <v>1847.270527465789</v>
       </c>
       <c r="M25" t="n">
-        <v>1674.995364432911</v>
+        <v>1674.915364432911</v>
       </c>
       <c r="N25" t="n">
-        <v>1451.576096481714</v>
+        <v>1451.496096481714</v>
       </c>
       <c r="O25" t="n">
-        <v>1158.196738826143</v>
+        <v>1158.116738826143</v>
       </c>
       <c r="P25" t="n">
-        <v>817.3402768783884</v>
+        <v>817.2602768783884</v>
       </c>
       <c r="Q25" t="n">
-        <v>437.7046542262692</v>
+        <v>437.6246542262692</v>
       </c>
       <c r="R25" t="n">
-        <v>57.29846434631862</v>
+        <v>57.21846434631862</v>
       </c>
       <c r="S25" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="T25" t="n">
-        <v>183.3756791588049</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U25" t="n">
-        <v>380.4268717970915</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V25" t="n">
-        <v>529.7482646830374</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W25" t="n">
-        <v>652.1391829427148</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X25" t="n">
-        <v>753.6699739669083</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y25" t="n">
-        <v>815.5792746459406</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="26">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>429.4804881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C26" t="n">
-        <v>329.0011162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D26" t="n">
-        <v>268.052474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E26" t="n">
-        <v>213.1400603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F26" t="n">
-        <v>157.695990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G26" t="n">
-        <v>103.3956148520479</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H26" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="I26" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="J26" t="n">
-        <v>436.1091130376557</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="K26" t="n">
-        <v>990.5091130376557</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="L26" t="n">
-        <v>1544.909113037656</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="M26" t="n">
-        <v>1801.400904947332</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="N26" t="n">
-        <v>1801.400904947332</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O26" t="n">
-        <v>1801.400904947332</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P26" t="n">
-        <v>1801.400904947332</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q26" t="n">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="R26" t="n">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="S26" t="n">
-        <v>2093.688719391593</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T26" t="n">
-        <v>1854.622475221327</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U26" t="n">
-        <v>1552.378741333841</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V26" t="n">
-        <v>1269.70093914513</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W26" t="n">
-        <v>978.4145997704354</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X26" t="n">
-        <v>733.6854750626902</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y26" t="n">
-        <v>562.8131275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>119.3229040110727</v>
+        <v>409.4673863086053</v>
       </c>
       <c r="C27" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="D27" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="E27" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="F27" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="G27" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="H27" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="I27" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="J27" t="n">
-        <v>168.756520175299</v>
+        <v>168.6765201752989</v>
       </c>
       <c r="K27" t="n">
-        <v>357.9493362696824</v>
+        <v>357.8693362696823</v>
       </c>
       <c r="L27" t="n">
-        <v>629.2997978648825</v>
+        <v>629.2197978648824</v>
       </c>
       <c r="M27" t="n">
-        <v>715.3803396077418</v>
+        <v>715.3003396077416</v>
       </c>
       <c r="N27" t="n">
-        <v>848.6606242153101</v>
+        <v>848.58062421531</v>
       </c>
       <c r="O27" t="n">
-        <v>1087.703075899029</v>
+        <v>1087.623075899029</v>
       </c>
       <c r="P27" t="n">
-        <v>1200.232420368536</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="Q27" t="n">
-        <v>1200.232420368536</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R27" t="n">
-        <v>1000.965958457041</v>
+        <v>937.5750872192206</v>
       </c>
       <c r="S27" t="n">
-        <v>883.2245443513734</v>
+        <v>819.8336731135525</v>
       </c>
       <c r="T27" t="n">
-        <v>827.3076097882282</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U27" t="n">
-        <v>776.5900746769285</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V27" t="n">
-        <v>711.4277845844838</v>
+        <v>648.0369133466629</v>
       </c>
       <c r="W27" t="n">
-        <v>628.2225897260712</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X27" t="n">
-        <v>557.6541660438616</v>
+        <v>494.2632948060406</v>
       </c>
       <c r="Y27" t="n">
-        <v>154.22851678514</v>
+        <v>444.3729990826726</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>870.1258296400258</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C28" t="n">
-        <v>946.6278354584616</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D28" t="n">
-        <v>1010.446979583462</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E28" t="n">
-        <v>1078.775883794875</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F28" t="n">
-        <v>1153.63685638681</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G28" t="n">
-        <v>1257.543422273696</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H28" t="n">
-        <v>1377.560007433093</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I28" t="n">
-        <v>1549.192886369176</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J28" t="n">
-        <v>1860.776627021628</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K28" t="n">
-        <v>1921.641060958496</v>
+        <v>1921.561060958496</v>
       </c>
       <c r="L28" t="n">
-        <v>1847.35052746579</v>
+        <v>1847.270527465789</v>
       </c>
       <c r="M28" t="n">
-        <v>1674.995364432911</v>
+        <v>1674.915364432911</v>
       </c>
       <c r="N28" t="n">
-        <v>1451.576096481714</v>
+        <v>1451.496096481714</v>
       </c>
       <c r="O28" t="n">
-        <v>1158.196738826143</v>
+        <v>1158.116738826143</v>
       </c>
       <c r="P28" t="n">
-        <v>817.3402768783884</v>
+        <v>817.2602768783884</v>
       </c>
       <c r="Q28" t="n">
-        <v>437.7046542262692</v>
+        <v>437.6246542262692</v>
       </c>
       <c r="R28" t="n">
-        <v>57.29846434631862</v>
+        <v>57.21846434631862</v>
       </c>
       <c r="S28" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="T28" t="n">
-        <v>175.6648964865979</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U28" t="n">
-        <v>372.7160891248845</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V28" t="n">
-        <v>522.0374820108304</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W28" t="n">
-        <v>644.4284002705078</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X28" t="n">
-        <v>745.9591912947013</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y28" t="n">
-        <v>807.8684919737336</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>437.4059340138206</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C29" t="n">
-        <v>336.9265620512004</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D29" t="n">
-        <v>275.977919889736</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E29" t="n">
-        <v>221.0655061454243</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F29" t="n">
-        <v>165.6214367433921</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G29" t="n">
-        <v>111.3210606959009</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H29" t="n">
-        <v>44.8</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I29" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="J29" t="n">
-        <v>44.8</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>181.7520762183974</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L29" t="n">
-        <v>181.7520762183974</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M29" t="n">
-        <v>692.6009049473324</v>
+        <v>1682.59</v>
       </c>
       <c r="N29" t="n">
-        <v>1247.000904947332</v>
+        <v>1682.59</v>
       </c>
       <c r="O29" t="n">
-        <v>1247.000904947332</v>
+        <v>2236</v>
       </c>
       <c r="P29" t="n">
-        <v>1801.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q29" t="n">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="R29" t="n">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="S29" t="n">
-        <v>2093.688719391593</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T29" t="n">
-        <v>1854.622475221327</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U29" t="n">
-        <v>1552.378741333841</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V29" t="n">
-        <v>1269.70093914513</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W29" t="n">
-        <v>978.4145997704354</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X29" t="n">
-        <v>733.6854750626902</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y29" t="n">
-        <v>570.7385733628857</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>119.3229040110726</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C30" t="n">
-        <v>108.1108712378208</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D30" t="n">
-        <v>108.1108712378208</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E30" t="n">
-        <v>108.1108712378208</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="F30" t="n">
-        <v>108.1108712378208</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="G30" t="n">
-        <v>44.8</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H30" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="I30" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="J30" t="n">
-        <v>168.756520175299</v>
+        <v>168.6765201752989</v>
       </c>
       <c r="K30" t="n">
-        <v>357.9493362696824</v>
+        <v>357.8693362696823</v>
       </c>
       <c r="L30" t="n">
-        <v>629.2997978648825</v>
+        <v>629.2197978648824</v>
       </c>
       <c r="M30" t="n">
-        <v>715.3803396077418</v>
+        <v>715.3003396077416</v>
       </c>
       <c r="N30" t="n">
-        <v>848.6606242153101</v>
+        <v>848.58062421531</v>
       </c>
       <c r="O30" t="n">
-        <v>1087.703075899029</v>
+        <v>1087.623075899029</v>
       </c>
       <c r="P30" t="n">
-        <v>1200.232420368536</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="Q30" t="n">
-        <v>1200.232420368536</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R30" t="n">
-        <v>1000.965958457041</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S30" t="n">
-        <v>883.2245443513734</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T30" t="n">
-        <v>473.7722562528746</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U30" t="n">
-        <v>423.0547211415748</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V30" t="n">
-        <v>357.8924310491302</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W30" t="n">
-        <v>274.6872361907176</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X30" t="n">
-        <v>204.1188125085079</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y30" t="n">
-        <v>154.2285167851399</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>870.1258296400258</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C31" t="n">
-        <v>946.6278354584616</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D31" t="n">
-        <v>1010.446979583462</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E31" t="n">
-        <v>1078.775883794875</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F31" t="n">
-        <v>1153.63685638681</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G31" t="n">
-        <v>1257.543422273696</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H31" t="n">
-        <v>1377.560007433093</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I31" t="n">
-        <v>1549.192886369176</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J31" t="n">
-        <v>1860.776627021628</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K31" t="n">
-        <v>1921.641060958496</v>
+        <v>1921.561060958496</v>
       </c>
       <c r="L31" t="n">
-        <v>1847.35052746579</v>
+        <v>1847.270527465789</v>
       </c>
       <c r="M31" t="n">
-        <v>1674.995364432911</v>
+        <v>1674.915364432911</v>
       </c>
       <c r="N31" t="n">
-        <v>1451.576096481714</v>
+        <v>1451.496096481714</v>
       </c>
       <c r="O31" t="n">
-        <v>1158.196738826143</v>
+        <v>1158.116738826143</v>
       </c>
       <c r="P31" t="n">
-        <v>817.3402768783884</v>
+        <v>817.2602768783884</v>
       </c>
       <c r="Q31" t="n">
-        <v>437.7046542262692</v>
+        <v>437.6246542262692</v>
       </c>
       <c r="R31" t="n">
-        <v>57.29846434631862</v>
+        <v>57.21846434631862</v>
       </c>
       <c r="S31" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="T31" t="n">
-        <v>175.6648964865979</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U31" t="n">
-        <v>372.7160891248845</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V31" t="n">
-        <v>522.0374820108304</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W31" t="n">
-        <v>644.4284002705078</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X31" t="n">
-        <v>745.9591912947013</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y31" t="n">
-        <v>807.8684919737336</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>437.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C32" t="n">
-        <v>336.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D32" t="n">
-        <v>268.052474045883</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E32" t="n">
-        <v>213.1400603015712</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F32" t="n">
-        <v>157.695990899539</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G32" t="n">
-        <v>103.3956148520479</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H32" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="I32" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="J32" t="n">
-        <v>44.8</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>44.8</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L32" t="n">
-        <v>599.2</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M32" t="n">
-        <v>599.2</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="N32" t="n">
-        <v>692.6009049473324</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O32" t="n">
-        <v>1247.000904947332</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P32" t="n">
-        <v>1801.400904947332</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q32" t="n">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="R32" t="n">
-        <v>2240</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S32" t="n">
-        <v>2093.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T32" t="n">
-        <v>1854.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U32" t="n">
-        <v>1552.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V32" t="n">
-        <v>1269.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W32" t="n">
-        <v>978.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X32" t="n">
-        <v>733.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y32" t="n">
-        <v>570.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>472.8582575464263</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C33" t="n">
-        <v>461.6462247731745</v>
+        <v>396.1722089875784</v>
       </c>
       <c r="D33" t="n">
-        <v>461.6462247731745</v>
+        <v>44.72</v>
       </c>
       <c r="E33" t="n">
-        <v>461.6462247731745</v>
+        <v>44.72</v>
       </c>
       <c r="F33" t="n">
-        <v>373.8298342171994</v>
+        <v>44.72</v>
       </c>
       <c r="G33" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="H33" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="I33" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="J33" t="n">
-        <v>168.756520175299</v>
+        <v>168.6765201752989</v>
       </c>
       <c r="K33" t="n">
-        <v>357.9493362696824</v>
+        <v>357.8693362696823</v>
       </c>
       <c r="L33" t="n">
-        <v>629.2997978648825</v>
+        <v>629.2197978648824</v>
       </c>
       <c r="M33" t="n">
-        <v>715.3803396077418</v>
+        <v>715.3003396077416</v>
       </c>
       <c r="N33" t="n">
-        <v>848.6606242153101</v>
+        <v>848.58062421531</v>
       </c>
       <c r="O33" t="n">
-        <v>1087.703075899029</v>
+        <v>1087.623075899029</v>
       </c>
       <c r="P33" t="n">
-        <v>1200.232420368536</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>1200.232420368536</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R33" t="n">
-        <v>1000.965958457041</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S33" t="n">
-        <v>883.2245443513734</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T33" t="n">
-        <v>827.3076097882282</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U33" t="n">
-        <v>776.5900746769285</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V33" t="n">
-        <v>711.4277845844838</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W33" t="n">
-        <v>628.2225897260712</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X33" t="n">
-        <v>557.6541660438616</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y33" t="n">
-        <v>507.7638703204935</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>870.1258296400258</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C34" t="n">
-        <v>946.6278354584616</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D34" t="n">
-        <v>1010.446979583462</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E34" t="n">
-        <v>1078.775883794875</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F34" t="n">
-        <v>1153.63685638681</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G34" t="n">
-        <v>1257.543422273696</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H34" t="n">
-        <v>1377.560007433093</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I34" t="n">
-        <v>1549.192886369176</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J34" t="n">
-        <v>1860.776627021628</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K34" t="n">
-        <v>1921.641060958496</v>
+        <v>1921.561060958496</v>
       </c>
       <c r="L34" t="n">
-        <v>1847.35052746579</v>
+        <v>1847.270527465789</v>
       </c>
       <c r="M34" t="n">
-        <v>1674.995364432911</v>
+        <v>1674.915364432911</v>
       </c>
       <c r="N34" t="n">
-        <v>1451.576096481714</v>
+        <v>1451.496096481714</v>
       </c>
       <c r="O34" t="n">
-        <v>1158.196738826143</v>
+        <v>1158.116738826143</v>
       </c>
       <c r="P34" t="n">
-        <v>817.3402768783884</v>
+        <v>817.2602768783884</v>
       </c>
       <c r="Q34" t="n">
-        <v>437.7046542262692</v>
+        <v>437.6246542262692</v>
       </c>
       <c r="R34" t="n">
-        <v>57.29846434631862</v>
+        <v>57.21846434631862</v>
       </c>
       <c r="S34" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="T34" t="n">
-        <v>183.3756791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U34" t="n">
-        <v>380.4268717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V34" t="n">
-        <v>529.7482646830374</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W34" t="n">
-        <v>652.1391829427148</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X34" t="n">
-        <v>745.9591912947013</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y34" t="n">
-        <v>807.8684919737336</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>429.4804881699675</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C35" t="n">
-        <v>329.0011162073474</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D35" t="n">
-        <v>268.052474045883</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E35" t="n">
-        <v>213.1400603015712</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F35" t="n">
-        <v>157.695990899539</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G35" t="n">
-        <v>103.3956148520479</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H35" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="I35" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="J35" t="n">
-        <v>436.1091130376557</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K35" t="n">
-        <v>576.8</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L35" t="n">
-        <v>1131.2</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M35" t="n">
-        <v>1131.2</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="N35" t="n">
-        <v>1685.6</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="O35" t="n">
-        <v>1685.6</v>
+        <v>2236</v>
       </c>
       <c r="P35" t="n">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="Q35" t="n">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="R35" t="n">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="S35" t="n">
-        <v>2085.76327354774</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T35" t="n">
-        <v>1846.697029377473</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U35" t="n">
-        <v>1544.453295489988</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V35" t="n">
-        <v>1261.775493301277</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W35" t="n">
-        <v>970.4891539265824</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X35" t="n">
-        <v>725.7600292188372</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y35" t="n">
-        <v>562.8131275190327</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>472.8582575464263</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C36" t="n">
-        <v>461.6462247731745</v>
+        <v>44.72</v>
       </c>
       <c r="D36" t="n">
-        <v>461.6462247731745</v>
+        <v>44.72</v>
       </c>
       <c r="E36" t="n">
-        <v>373.8298342171994</v>
+        <v>44.72</v>
       </c>
       <c r="F36" t="n">
-        <v>373.8298342171994</v>
+        <v>44.72</v>
       </c>
       <c r="G36" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="H36" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="I36" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="J36" t="n">
-        <v>168.756520175299</v>
+        <v>168.6765201752989</v>
       </c>
       <c r="K36" t="n">
-        <v>357.9493362696824</v>
+        <v>357.8693362696823</v>
       </c>
       <c r="L36" t="n">
-        <v>629.2997978648825</v>
+        <v>629.2197978648824</v>
       </c>
       <c r="M36" t="n">
-        <v>715.3803396077418</v>
+        <v>715.3003396077416</v>
       </c>
       <c r="N36" t="n">
-        <v>848.6606242153101</v>
+        <v>848.58062421531</v>
       </c>
       <c r="O36" t="n">
-        <v>1087.703075899029</v>
+        <v>1087.623075899029</v>
       </c>
       <c r="P36" t="n">
-        <v>1200.232420368536</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="Q36" t="n">
-        <v>1200.232420368536</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R36" t="n">
-        <v>1000.965958457041</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S36" t="n">
-        <v>883.2245443513734</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T36" t="n">
-        <v>827.3076097882282</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U36" t="n">
-        <v>776.5900746769285</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V36" t="n">
-        <v>711.4277845844838</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W36" t="n">
-        <v>628.2225897260712</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X36" t="n">
-        <v>557.6541660438616</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y36" t="n">
-        <v>507.7638703204935</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>870.1258296400258</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C37" t="n">
-        <v>946.6278354584616</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D37" t="n">
-        <v>1010.446979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E37" t="n">
-        <v>1078.775883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F37" t="n">
-        <v>1153.63685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G37" t="n">
-        <v>1257.543422273696</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H37" t="n">
-        <v>1377.560007433093</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I37" t="n">
-        <v>1549.192886369176</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J37" t="n">
-        <v>1860.776627021628</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K37" t="n">
-        <v>1921.641060958496</v>
+        <v>1921.561060958496</v>
       </c>
       <c r="L37" t="n">
-        <v>1847.35052746579</v>
+        <v>1847.270527465789</v>
       </c>
       <c r="M37" t="n">
-        <v>1674.995364432911</v>
+        <v>1674.915364432911</v>
       </c>
       <c r="N37" t="n">
-        <v>1451.576096481714</v>
+        <v>1451.496096481714</v>
       </c>
       <c r="O37" t="n">
-        <v>1158.196738826143</v>
+        <v>1158.116738826143</v>
       </c>
       <c r="P37" t="n">
-        <v>817.3402768783884</v>
+        <v>817.2602768783884</v>
       </c>
       <c r="Q37" t="n">
-        <v>437.7046542262692</v>
+        <v>437.6246542262692</v>
       </c>
       <c r="R37" t="n">
-        <v>57.29846434631862</v>
+        <v>57.21846434631862</v>
       </c>
       <c r="S37" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="T37" t="n">
-        <v>183.3756791588049</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U37" t="n">
-        <v>380.4268717970915</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V37" t="n">
-        <v>522.0374820108304</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W37" t="n">
-        <v>644.4284002705078</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X37" t="n">
-        <v>745.9591912947013</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y37" t="n">
-        <v>807.8684919737336</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>429.4804881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C38" t="n">
-        <v>329.0011162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D38" t="n">
-        <v>268.052474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E38" t="n">
-        <v>213.1400603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F38" t="n">
-        <v>157.695990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G38" t="n">
-        <v>103.3956148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H38" t="n">
-        <v>44.8</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I38" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="J38" t="n">
-        <v>436.1091130376557</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>436.1091130376557</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L38" t="n">
-        <v>990.5091130376557</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M38" t="n">
-        <v>1247.000904947332</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N38" t="n">
-        <v>1801.400904947332</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O38" t="n">
-        <v>1801.400904947332</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P38" t="n">
-        <v>1801.400904947332</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q38" t="n">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="R38" t="n">
-        <v>2232.074554156147</v>
+        <v>2236</v>
       </c>
       <c r="S38" t="n">
-        <v>2085.76327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T38" t="n">
-        <v>1846.697029377473</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U38" t="n">
-        <v>1544.453295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V38" t="n">
-        <v>1261.775493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W38" t="n">
-        <v>970.4891539265824</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X38" t="n">
-        <v>725.7600292188372</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y38" t="n">
-        <v>562.8131275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>399.0789442256527</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C39" t="n">
-        <v>387.8669114524009</v>
+        <v>44.72</v>
       </c>
       <c r="D39" t="n">
-        <v>387.8669114524009</v>
+        <v>44.72</v>
       </c>
       <c r="E39" t="n">
-        <v>387.8669114524009</v>
+        <v>44.72</v>
       </c>
       <c r="F39" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="G39" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="H39" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="I39" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="J39" t="n">
-        <v>168.756520175299</v>
+        <v>168.6765201752989</v>
       </c>
       <c r="K39" t="n">
-        <v>357.9493362696824</v>
+        <v>357.8693362696823</v>
       </c>
       <c r="L39" t="n">
-        <v>629.2997978648825</v>
+        <v>629.2197978648824</v>
       </c>
       <c r="M39" t="n">
-        <v>715.3803396077418</v>
+        <v>715.3003396077416</v>
       </c>
       <c r="N39" t="n">
-        <v>848.6606242153101</v>
+        <v>848.58062421531</v>
       </c>
       <c r="O39" t="n">
-        <v>1087.703075899029</v>
+        <v>1087.623075899029</v>
       </c>
       <c r="P39" t="n">
-        <v>1200.232420368536</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="Q39" t="n">
-        <v>1200.232420368536</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R39" t="n">
-        <v>1000.965958457041</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S39" t="n">
-        <v>883.2245443513734</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T39" t="n">
-        <v>827.3076097882282</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U39" t="n">
-        <v>776.5900746769285</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V39" t="n">
-        <v>711.4277845844838</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W39" t="n">
-        <v>628.2225897260712</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X39" t="n">
-        <v>557.6541660438616</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y39" t="n">
-        <v>507.7638703204935</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>870.1258296400258</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C40" t="n">
-        <v>946.6278354584616</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D40" t="n">
-        <v>1010.446979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E40" t="n">
-        <v>1078.775883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F40" t="n">
-        <v>1153.63685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G40" t="n">
-        <v>1257.543422273696</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H40" t="n">
-        <v>1377.560007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I40" t="n">
-        <v>1549.192886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J40" t="n">
-        <v>1860.776627021628</v>
+        <v>1868.407409693835</v>
       </c>
       <c r="K40" t="n">
-        <v>1921.641060958496</v>
+        <v>1921.561060958496</v>
       </c>
       <c r="L40" t="n">
-        <v>1847.35052746579</v>
+        <v>1847.270527465789</v>
       </c>
       <c r="M40" t="n">
-        <v>1674.995364432911</v>
+        <v>1674.915364432911</v>
       </c>
       <c r="N40" t="n">
-        <v>1451.576096481714</v>
+        <v>1451.496096481714</v>
       </c>
       <c r="O40" t="n">
-        <v>1158.196738826143</v>
+        <v>1158.116738826143</v>
       </c>
       <c r="P40" t="n">
-        <v>817.3402768783884</v>
+        <v>817.2602768783884</v>
       </c>
       <c r="Q40" t="n">
-        <v>437.7046542262692</v>
+        <v>437.6246542262692</v>
       </c>
       <c r="R40" t="n">
-        <v>57.29846434631862</v>
+        <v>57.21846434631862</v>
       </c>
       <c r="S40" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="T40" t="n">
-        <v>183.3756791588049</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U40" t="n">
-        <v>380.4268717970915</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V40" t="n">
-        <v>529.7482646830374</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W40" t="n">
-        <v>652.1391829427148</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X40" t="n">
-        <v>753.6699739669083</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y40" t="n">
-        <v>815.5792746459406</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>429.4804881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C41" t="n">
-        <v>329.0011162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D41" t="n">
-        <v>268.052474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E41" t="n">
-        <v>213.1400603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F41" t="n">
-        <v>157.695990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G41" t="n">
-        <v>103.3956148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H41" t="n">
-        <v>44.8</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I41" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="J41" t="n">
-        <v>44.8</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>44.8</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L41" t="n">
-        <v>44.8</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M41" t="n">
-        <v>555.648828728935</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N41" t="n">
-        <v>1110.048828728935</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O41" t="n">
-        <v>1247.000904947332</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P41" t="n">
-        <v>1801.400904947332</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q41" t="n">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="R41" t="n">
-        <v>2232.074554156147</v>
+        <v>2236</v>
       </c>
       <c r="S41" t="n">
-        <v>2085.76327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T41" t="n">
-        <v>1846.697029377473</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U41" t="n">
-        <v>1544.453295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V41" t="n">
-        <v>1261.775493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W41" t="n">
-        <v>970.4891539265824</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X41" t="n">
-        <v>725.7600292188372</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y41" t="n">
-        <v>562.8131275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>56.01203277325182</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C42" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="D42" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="E42" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="F42" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="G42" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="H42" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="I42" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="J42" t="n">
-        <v>168.756520175299</v>
+        <v>168.6765201752989</v>
       </c>
       <c r="K42" t="n">
-        <v>357.9493362696824</v>
+        <v>357.8693362696823</v>
       </c>
       <c r="L42" t="n">
-        <v>629.2997978648825</v>
+        <v>629.2197978648824</v>
       </c>
       <c r="M42" t="n">
-        <v>715.3803396077418</v>
+        <v>715.3003396077416</v>
       </c>
       <c r="N42" t="n">
-        <v>848.6606242153101</v>
+        <v>848.58062421531</v>
       </c>
       <c r="O42" t="n">
-        <v>1087.703075899029</v>
+        <v>1087.623075899029</v>
       </c>
       <c r="P42" t="n">
-        <v>1200.232420368536</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="Q42" t="n">
-        <v>1200.232420368536</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R42" t="n">
-        <v>1000.965958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S42" t="n">
-        <v>883.2245443513734</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T42" t="n">
-        <v>827.3076097882282</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U42" t="n">
-        <v>776.5900746769285</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V42" t="n">
-        <v>648.1169133466631</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W42" t="n">
-        <v>564.9117184882504</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X42" t="n">
-        <v>494.3432948060407</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y42" t="n">
-        <v>90.9176455473191</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>870.1258296400258</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C43" t="n">
-        <v>946.6278354584616</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D43" t="n">
-        <v>1010.446979583462</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E43" t="n">
-        <v>1078.775883794875</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F43" t="n">
-        <v>1153.63685638681</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G43" t="n">
-        <v>1257.543422273696</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H43" t="n">
-        <v>1377.560007433093</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I43" t="n">
-        <v>1549.192886369176</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J43" t="n">
-        <v>1860.776627021628</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K43" t="n">
-        <v>1921.641060958496</v>
+        <v>1921.561060958496</v>
       </c>
       <c r="L43" t="n">
-        <v>1847.35052746579</v>
+        <v>1847.270527465789</v>
       </c>
       <c r="M43" t="n">
-        <v>1674.995364432911</v>
+        <v>1674.915364432911</v>
       </c>
       <c r="N43" t="n">
-        <v>1451.576096481714</v>
+        <v>1451.496096481714</v>
       </c>
       <c r="O43" t="n">
-        <v>1158.196738826143</v>
+        <v>1158.116738826143</v>
       </c>
       <c r="P43" t="n">
-        <v>817.3402768783884</v>
+        <v>817.2602768783884</v>
       </c>
       <c r="Q43" t="n">
-        <v>437.7046542262692</v>
+        <v>437.6246542262692</v>
       </c>
       <c r="R43" t="n">
-        <v>57.29846434631862</v>
+        <v>57.21846434631862</v>
       </c>
       <c r="S43" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="T43" t="n">
-        <v>175.6648964865979</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U43" t="n">
-        <v>372.7160891248845</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V43" t="n">
-        <v>522.0374820108304</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W43" t="n">
-        <v>644.4284002705078</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X43" t="n">
-        <v>745.9591912947013</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y43" t="n">
-        <v>807.8684919737336</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>437.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C44" t="n">
-        <v>336.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D44" t="n">
-        <v>275.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E44" t="n">
-        <v>221.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F44" t="n">
-        <v>165.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G44" t="n">
-        <v>111.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H44" t="n">
-        <v>52.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I44" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>44.8</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K44" t="n">
-        <v>599.2</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L44" t="n">
-        <v>1153.6</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M44" t="n">
-        <v>1664.448828728935</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N44" t="n">
-        <v>2218.848828728935</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O44" t="n">
-        <v>2218.848828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P44" t="n">
-        <v>2218.848828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q44" t="n">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="R44" t="n">
-        <v>2240</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S44" t="n">
-        <v>2093.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T44" t="n">
-        <v>1854.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U44" t="n">
-        <v>1552.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V44" t="n">
-        <v>1269.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W44" t="n">
-        <v>978.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X44" t="n">
-        <v>733.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y44" t="n">
-        <v>570.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>407.4642417608302</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C45" t="n">
-        <v>396.2522089875785</v>
+        <v>44.72</v>
       </c>
       <c r="D45" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="E45" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="F45" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="G45" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="H45" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="I45" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="J45" t="n">
-        <v>168.756520175299</v>
+        <v>168.6765201752989</v>
       </c>
       <c r="K45" t="n">
-        <v>357.9493362696824</v>
+        <v>357.8693362696823</v>
       </c>
       <c r="L45" t="n">
-        <v>629.2997978648825</v>
+        <v>629.2197978648824</v>
       </c>
       <c r="M45" t="n">
-        <v>715.3803396077418</v>
+        <v>715.3003396077416</v>
       </c>
       <c r="N45" t="n">
-        <v>848.6606242153101</v>
+        <v>848.58062421531</v>
       </c>
       <c r="O45" t="n">
-        <v>1087.703075899029</v>
+        <v>1087.623075899029</v>
       </c>
       <c r="P45" t="n">
-        <v>1200.232420368536</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="Q45" t="n">
-        <v>1200.232420368536</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R45" t="n">
-        <v>1000.965958457041</v>
+        <v>937.5750872192206</v>
       </c>
       <c r="S45" t="n">
-        <v>883.2245443513734</v>
+        <v>819.8336731135525</v>
       </c>
       <c r="T45" t="n">
-        <v>827.3076097882282</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U45" t="n">
-        <v>776.5900746769285</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V45" t="n">
-        <v>646.0337687988879</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W45" t="n">
-        <v>562.8285739404752</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X45" t="n">
-        <v>492.2601502582655</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y45" t="n">
-        <v>442.3698545348975</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>877.8366123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C46" t="n">
-        <v>954.3386181306686</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D46" t="n">
-        <v>1018.157762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E46" t="n">
-        <v>1086.486666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F46" t="n">
-        <v>1161.347639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G46" t="n">
-        <v>1265.254204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H46" t="n">
-        <v>1385.2707901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I46" t="n">
-        <v>1556.903669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J46" t="n">
-        <v>1860.776627021628</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K46" t="n">
-        <v>1921.641060958496</v>
+        <v>1921.561060958496</v>
       </c>
       <c r="L46" t="n">
-        <v>1847.35052746579</v>
+        <v>1847.270527465789</v>
       </c>
       <c r="M46" t="n">
-        <v>1674.995364432911</v>
+        <v>1674.915364432911</v>
       </c>
       <c r="N46" t="n">
-        <v>1451.576096481714</v>
+        <v>1451.496096481714</v>
       </c>
       <c r="O46" t="n">
-        <v>1158.196738826143</v>
+        <v>1158.116738826143</v>
       </c>
       <c r="P46" t="n">
-        <v>817.3402768783884</v>
+        <v>817.2602768783884</v>
       </c>
       <c r="Q46" t="n">
-        <v>437.7046542262692</v>
+        <v>437.6246542262692</v>
       </c>
       <c r="R46" t="n">
-        <v>57.29846434631862</v>
+        <v>57.21846434631862</v>
       </c>
       <c r="S46" t="n">
-        <v>44.8</v>
+        <v>44.72</v>
       </c>
       <c r="T46" t="n">
-        <v>183.3756791588049</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U46" t="n">
-        <v>380.4268717970915</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V46" t="n">
-        <v>529.7482646830374</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W46" t="n">
-        <v>652.1391829427148</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X46" t="n">
-        <v>753.6699739669083</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y46" t="n">
-        <v>815.5792746459406</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
   </sheetData>
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7973,7 +7973,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>544.2621276423173</v>
+        <v>948.2520266322164</v>
       </c>
       <c r="N2" t="n">
         <v>898.2489580698352</v>
@@ -7982,10 +7982,10 @@
         <v>491.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>9.015228689513952</v>
+        <v>421.2870600406814</v>
       </c>
       <c r="Q2" t="n">
-        <v>593.8226843274854</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8204,25 +8204,25 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>403.9898989898991</v>
       </c>
       <c r="M5" t="n">
         <v>965.2621276423173</v>
       </c>
       <c r="N5" t="n">
-        <v>898.2489580698352</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O5" t="n">
-        <v>491.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P5" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q5" t="n">
-        <v>576.8125833173845</v>
+        <v>593.8226843274854</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8441,7 +8441,7 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>403.9898989898991</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -8459,7 +8459,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
-        <v>576.8125833173845</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,10 +8675,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>173.3784367687241</v>
+        <v>55.44822975121687</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -8687,16 +8687,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
-        <v>1037.248958069835</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O11" t="n">
-        <v>630.2478695740924</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P11" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,10 +8912,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -8924,16 +8924,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
-        <v>1037.248958069835</v>
+        <v>777.3630622928068</v>
       </c>
       <c r="O14" t="n">
-        <v>630.2478695740924</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P14" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q14" t="n">
-        <v>194.1875037932075</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,19 +9149,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="L17" t="n">
-        <v>559.9999999999999</v>
+        <v>559</v>
       </c>
       <c r="M17" t="n">
-        <v>638.6064760739663</v>
+        <v>685.4145387153924</v>
       </c>
       <c r="N17" t="n">
-        <v>1037.248958069835</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O17" t="n">
         <v>70.24786957409245</v>
@@ -9170,7 +9170,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,10 +9386,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>20.40522350612657</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -9398,16 +9398,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>1037.248958069835</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O20" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P20" t="n">
-        <v>303.360760223249</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,25 +9623,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>56.40782571081238</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>560</v>
+        <v>184.1434931650601</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>1037.248958069835</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O23" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P23" t="n">
-        <v>560.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q23" t="n">
         <v>172.8226843274854</v>
@@ -9860,25 +9860,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>430.3047365861567</v>
+        <v>171.4188408091284</v>
       </c>
       <c r="K26" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>560.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>803.3447457328998</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O26" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10097,28 +10097,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>138.3354305236338</v>
+        <v>559</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M29" t="n">
-        <v>1060.271045550332</v>
+        <v>685.4145387153924</v>
       </c>
       <c r="N29" t="n">
-        <v>1037.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O29" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P29" t="n">
-        <v>560.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,25 +10334,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L32" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>571.5933065014841</v>
+        <v>777.3630622928066</v>
       </c>
       <c r="O32" t="n">
-        <v>630.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P32" t="n">
-        <v>560.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q32" t="n">
         <v>615.8520732695737</v>
@@ -10574,22 +10574,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>142.1120070326709</v>
+        <v>559</v>
       </c>
       <c r="L35" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>1037.248958069835</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O35" t="n">
-        <v>70.24786957409245</v>
+        <v>254.3913627391524</v>
       </c>
       <c r="P35" t="n">
-        <v>560.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
         <v>172.8226843274854</v>
@@ -10814,16 +10814,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>803.3447457328998</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>1037.248958069835</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O38" t="n">
-        <v>70.24786957409245</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P38" t="n">
         <v>0.2870600406814136</v>
@@ -11045,7 +11045,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -11057,13 +11057,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>1037.248958069835</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O41" t="n">
-        <v>208.5833000977262</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P41" t="n">
-        <v>560.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
         <v>615.8520732695737</v>
@@ -11282,28 +11282,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>559.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>1037.248958069835</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O44" t="n">
-        <v>70.24786957409245</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P44" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
-        <v>194.1875037932075</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3463769.483214569</v>
+        <v>3463722.205638811</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4313848.985439071</v>
+        <v>4313801.707863313</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5163928.487663573</v>
+        <v>5163881.210087814</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6014007.989888071</v>
+        <v>6013960.712312313</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6864087.492112569</v>
+        <v>6864040.21453681</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7714166.994337067</v>
+        <v>7714119.716761309</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8564246.496561565</v>
+        <v>8564199.218985807</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9414325.998786068</v>
+        <v>9414278.72121031</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10264405.50101058</v>
+        <v>10264358.22343482</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11114485.00323508</v>
+        <v>11114437.72565933</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>11964564.50545959</v>
+        <v>11964517.22788383</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12814644.0076841</v>
+        <v>12814596.73010834</v>
       </c>
     </row>
   </sheetData>
@@ -26278,10 +26278,10 @@
         <v>1353830.31835754</v>
       </c>
       <c r="E2" t="n">
-        <v>1353830.31835754</v>
+        <v>1353830.318357541</v>
       </c>
       <c r="F2" t="n">
-        <v>1353830.31835754</v>
+        <v>1353830.318357541</v>
       </c>
       <c r="G2" t="n">
         <v>1353830.31835754</v>
@@ -26296,7 +26296,7 @@
         <v>1353830.31835754</v>
       </c>
       <c r="K2" t="n">
-        <v>1353830.31835754</v>
+        <v>1353830.318357541</v>
       </c>
       <c r="L2" t="n">
         <v>1353830.31835754</v>
@@ -26330,7 +26330,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>328928</v>
+        <v>328576</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26354,7 +26354,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>48928</v>
+        <v>48576</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>566354.9592425094</v>
+        <v>567917.5723359545</v>
       </c>
       <c r="C4" t="n">
-        <v>564322.4434789647</v>
+        <v>565885.0565724098</v>
       </c>
       <c r="D4" t="n">
-        <v>562287.1704809261</v>
+        <v>563849.7835743711</v>
       </c>
       <c r="E4" t="n">
-        <v>542968.9204048134</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541026.7377991641</v>
+        <v>542893.0076941387</v>
       </c>
       <c r="G4" t="n">
-        <v>539081.8750543876</v>
+        <v>540947.4312259532</v>
       </c>
       <c r="H4" t="n">
-        <v>537134.3129511029</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535184.0320195116</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>533231.0125346463</v>
+        <v>535094.4215636665</v>
       </c>
       <c r="K4" t="n">
-        <v>531275.2345115119</v>
+        <v>533137.9258114471</v>
       </c>
       <c r="L4" t="n">
-        <v>529316.6777000939</v>
+        <v>531178.6502511877</v>
       </c>
       <c r="M4" t="n">
-        <v>527355.3215802427</v>
+        <v>529216.5743552083</v>
       </c>
       <c r="N4" t="n">
-        <v>525391.1453564359</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523424.1279523974</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521454.2480055793</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26434,40 +26434,40 @@
         <v>59224.39999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>63472.15</v>
+        <v>63411.35</v>
       </c>
       <c r="F5" t="n">
-        <v>63472.15</v>
+        <v>63411.35</v>
       </c>
       <c r="G5" t="n">
-        <v>63472.15</v>
+        <v>63411.35</v>
       </c>
       <c r="H5" t="n">
-        <v>63472.15</v>
+        <v>63411.35</v>
       </c>
       <c r="I5" t="n">
-        <v>63472.15</v>
+        <v>63411.35</v>
       </c>
       <c r="J5" t="n">
-        <v>63472.15</v>
+        <v>63411.35</v>
       </c>
       <c r="K5" t="n">
-        <v>63472.15</v>
+        <v>63411.35</v>
       </c>
       <c r="L5" t="n">
-        <v>63472.15</v>
+        <v>63411.35</v>
       </c>
       <c r="M5" t="n">
-        <v>63472.15</v>
+        <v>63411.35</v>
       </c>
       <c r="N5" t="n">
-        <v>63472.15</v>
+        <v>63411.35</v>
       </c>
       <c r="O5" t="n">
-        <v>63472.15</v>
+        <v>63411.35</v>
       </c>
       <c r="P5" t="n">
-        <v>63472.15</v>
+        <v>63411.35</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>580058.9591150308</v>
+        <v>578496.3460215853</v>
       </c>
       <c r="C6" t="n">
-        <v>730283.4748785755</v>
+        <v>728720.8617851305</v>
       </c>
       <c r="D6" t="n">
-        <v>732318.7478766138</v>
+        <v>730756.1347831691</v>
       </c>
       <c r="E6" t="n">
-        <v>418461.2479527269</v>
+        <v>417007.0653178977</v>
       </c>
       <c r="F6" t="n">
-        <v>749331.4305583761</v>
+        <v>747525.9606634021</v>
       </c>
       <c r="G6" t="n">
-        <v>751276.2933031524</v>
+        <v>749471.5371315872</v>
       </c>
       <c r="H6" t="n">
-        <v>753223.8554064372</v>
+        <v>751419.8139488884</v>
       </c>
       <c r="I6" t="n">
-        <v>755174.1363380287</v>
+        <v>753370.8105922487</v>
       </c>
       <c r="J6" t="n">
-        <v>328935.155822894</v>
+        <v>327132.5467938735</v>
       </c>
       <c r="K6" t="n">
-        <v>759082.9338460284</v>
+        <v>757281.0425460935</v>
       </c>
       <c r="L6" t="n">
-        <v>761041.4906574461</v>
+        <v>759240.3181063526</v>
       </c>
       <c r="M6" t="n">
-        <v>714074.8467772971</v>
+        <v>712626.3940023315</v>
       </c>
       <c r="N6" t="n">
-        <v>764967.0230011039</v>
+        <v>763167.2910371854</v>
       </c>
       <c r="O6" t="n">
-        <v>486934.0404051429</v>
+        <v>485135.0302949235</v>
       </c>
       <c r="P6" t="n">
-        <v>768903.9203519608</v>
+        <v>767105.6331459337</v>
       </c>
     </row>
   </sheetData>
@@ -26868,40 +26868,40 @@
         <v>421</v>
       </c>
       <c r="E4" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="F4" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G4" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H4" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="I4" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="J4" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="K4" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="L4" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="M4" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="N4" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="O4" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="P4" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>
@@ -26972,49 +26972,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E2" t="n">
         <v>350</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>350</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>350</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
@@ -27027,7 +27027,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -27036,37 +27036,37 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -27079,25 +27079,25 @@
         <v>421</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E4" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J4" t="n">
         <v>421</v>
@@ -27109,16 +27109,16 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
@@ -27326,7 +27326,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -27442,7 +27442,7 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>400</v>
+        <v>231.5850086145855</v>
       </c>
       <c r="F2" t="n">
         <v>400</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>82.46360744287983</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27518,22 +27518,22 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>155.5878407271842</v>
       </c>
       <c r="E3" t="n">
-        <v>50.01054562754115</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27594,10 +27594,10 @@
         <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
@@ -27606,19 +27606,19 @@
         <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>400</v>
+        <v>304.7009855303386</v>
       </c>
       <c r="H4" t="n">
-        <v>251.6185868080527</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,7 +27642,7 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
         <v>400</v>
@@ -27654,7 +27654,7 @@
         <v>400</v>
       </c>
       <c r="W4" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X4" t="n">
         <v>400</v>
@@ -27676,13 +27676,13 @@
         <v>400</v>
       </c>
       <c r="D5" t="n">
-        <v>400</v>
+        <v>231.5850086145855</v>
       </c>
       <c r="E5" t="n">
         <v>400</v>
       </c>
       <c r="F5" t="n">
-        <v>231.5850086145855</v>
+        <v>400</v>
       </c>
       <c r="G5" t="n">
         <v>400</v>
@@ -27749,13 +27749,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -27794,16 +27794,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>274.7686191606065</v>
+        <v>126.2737972923793</v>
       </c>
       <c r="S6" t="n">
-        <v>400</v>
+        <v>45.5639999646113</v>
       </c>
       <c r="T6" t="n">
-        <v>400</v>
+        <v>343.5158434500662</v>
       </c>
       <c r="U6" t="n">
         <v>400</v>
@@ -27828,7 +27828,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
         <v>400</v>
@@ -27837,25 +27837,25 @@
         <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
+        <v>266.6291246284015</v>
+      </c>
+      <c r="H7" t="n">
         <v>400</v>
-      </c>
-      <c r="H7" t="n">
-        <v>228.7711261016186</v>
       </c>
       <c r="I7" t="n">
         <v>176.6334556201183</v>
       </c>
       <c r="J7" t="n">
+        <v>35.26894883590776</v>
+      </c>
+      <c r="K7" t="n">
         <v>400</v>
-      </c>
-      <c r="K7" t="n">
-        <v>288.520773801143</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27888,13 +27888,13 @@
         <v>150.9583912744579</v>
       </c>
       <c r="V7" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W7" t="n">
         <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>379.3029678452092</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
         <v>400</v>
@@ -27916,10 +27916,10 @@
         <v>400</v>
       </c>
       <c r="E8" t="n">
+        <v>381.6661682972702</v>
+      </c>
+      <c r="F8" t="n">
         <v>400</v>
-      </c>
-      <c r="F8" t="n">
-        <v>231.5850086145855</v>
       </c>
       <c r="G8" t="n">
         <v>400</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27998,13 +27998,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>139.8182410159027</v>
       </c>
       <c r="G9" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>217.1263858913485</v>
@@ -28040,16 +28040,16 @@
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="V9" t="n">
         <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>342.2743756165772</v>
+        <v>400</v>
       </c>
       <c r="X9" t="n">
         <v>400</v>
@@ -28071,28 +28071,28 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
         <v>400</v>
       </c>
       <c r="F10" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G10" t="n">
+        <v>245.04387284153</v>
+      </c>
+      <c r="H10" t="n">
         <v>400</v>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v>400</v>
       </c>
-      <c r="H10" t="n">
-        <v>228.7711261016186</v>
-      </c>
-      <c r="I10" t="n">
-        <v>176.6334556201183</v>
-      </c>
       <c r="J10" t="n">
-        <v>57.51550504132405</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>333.4977739464678</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28125,16 +28125,16 @@
         <v>400</v>
       </c>
       <c r="V10" t="n">
+        <v>199.1703102162162</v>
+      </c>
+      <c r="W10" t="n">
         <v>400</v>
-      </c>
-      <c r="W10" t="n">
-        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
         <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28165,7 +28165,7 @@
         <v>350</v>
       </c>
       <c r="I11" t="n">
-        <v>142.2349682972701</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28241,7 +28241,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H12" t="n">
-        <v>332.1680871864211</v>
+        <v>269.4903246609787</v>
       </c>
       <c r="I12" t="n">
         <v>217.1263858913485</v>
@@ -28274,7 +28274,7 @@
         <v>350</v>
       </c>
       <c r="S12" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>350</v>
@@ -28286,10 +28286,10 @@
         <v>350</v>
       </c>
       <c r="W12" t="n">
-        <v>287.3222374745574</v>
+        <v>350</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="Y12" t="n">
         <v>350</v>
@@ -28356,7 +28356,7 @@
         <v>350</v>
       </c>
       <c r="T13" t="n">
-        <v>342.2113306341344</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U13" t="n">
         <v>350</v>
@@ -28402,7 +28402,7 @@
         <v>350</v>
       </c>
       <c r="I14" t="n">
-        <v>142.2349682972701</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28463,7 +28463,7 @@
         <v>350</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D15" t="n">
         <v>347.9376868977026</v>
@@ -28475,13 +28475,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>332.1680871864211</v>
       </c>
       <c r="I15" t="n">
-        <v>154.4486233659059</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28508,7 +28508,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
-        <v>350</v>
+        <v>263.0617733495848</v>
       </c>
       <c r="S15" t="n">
         <v>350</v>
@@ -28593,7 +28593,7 @@
         <v>350</v>
       </c>
       <c r="T16" t="n">
-        <v>342.2113306341344</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U16" t="n">
         <v>350</v>
@@ -28636,10 +28636,10 @@
         <v>350</v>
       </c>
       <c r="H17" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I17" t="n">
-        <v>142.2349682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28697,7 +28697,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="C18" t="n">
         <v>350</v>
@@ -28706,7 +28706,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>279.99433469647</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
         <v>339.6362423378769</v>
@@ -28766,7 +28766,7 @@
         <v>350</v>
       </c>
       <c r="Y18" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -28830,13 +28830,13 @@
         <v>350</v>
       </c>
       <c r="T19" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U19" t="n">
         <v>350</v>
       </c>
       <c r="V19" t="n">
-        <v>342.2113306341344</v>
+        <v>350</v>
       </c>
       <c r="W19" t="n">
         <v>350</v>
@@ -28873,7 +28873,7 @@
         <v>350</v>
       </c>
       <c r="H20" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I20" t="n">
         <v>150.0811596826846</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>243.0324074428798</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S20" t="n">
         <v>350</v>
@@ -28943,7 +28943,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>262.1624218828911</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
         <v>339.6362423378769</v>
@@ -28952,7 +28952,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>269.4903246609787</v>
       </c>
       <c r="I21" t="n">
         <v>217.1263858913485</v>
@@ -28982,7 +28982,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R21" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>350</v>
@@ -29067,7 +29067,7 @@
         <v>350</v>
       </c>
       <c r="T22" t="n">
-        <v>342.2113306341344</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U22" t="n">
         <v>350</v>
@@ -29110,7 +29110,7 @@
         <v>350</v>
       </c>
       <c r="H23" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I23" t="n">
         <v>150.0811596826846</v>
@@ -29146,7 +29146,7 @@
         <v>350</v>
       </c>
       <c r="T23" t="n">
-        <v>342.1538086145853</v>
+        <v>350</v>
       </c>
       <c r="U23" t="n">
         <v>350</v>
@@ -29174,7 +29174,7 @@
         <v>350</v>
       </c>
       <c r="C24" t="n">
-        <v>287.3222374745574</v>
+        <v>350</v>
       </c>
       <c r="D24" t="n">
         <v>347.9376868977026</v>
@@ -29189,7 +29189,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H24" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>217.1263858913485</v>
@@ -29219,7 +29219,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
-        <v>350</v>
+        <v>269.4903246609786</v>
       </c>
       <c r="S24" t="n">
         <v>350</v>
@@ -29234,7 +29234,7 @@
         <v>350</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="X24" t="n">
         <v>350</v>
@@ -29265,7 +29265,7 @@
         <v>350</v>
       </c>
       <c r="G25" t="n">
-        <v>342.2113306341345</v>
+        <v>350</v>
       </c>
       <c r="H25" t="n">
         <v>350</v>
@@ -29274,7 +29274,7 @@
         <v>350</v>
       </c>
       <c r="J25" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="K25" t="n">
         <v>350</v>
@@ -29344,7 +29344,7 @@
         <v>350</v>
       </c>
       <c r="G26" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H26" t="n">
         <v>350</v>
@@ -29398,7 +29398,7 @@
         <v>350</v>
       </c>
       <c r="Y26" t="n">
-        <v>342.1538086145855</v>
+        <v>350</v>
       </c>
     </row>
     <row r="27">
@@ -29411,7 +29411,7 @@
         <v>350</v>
       </c>
       <c r="C27" t="n">
-        <v>287.3222374745574</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>347.9376868977026</v>
@@ -29456,7 +29456,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R27" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="S27" t="n">
         <v>350</v>
@@ -29477,7 +29477,7 @@
         <v>350</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="28">
@@ -29541,7 +29541,7 @@
         <v>350</v>
       </c>
       <c r="T28" t="n">
-        <v>342.2113306341344</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U28" t="n">
         <v>350</v>
@@ -29584,10 +29584,10 @@
         <v>350</v>
       </c>
       <c r="H29" t="n">
-        <v>342.1538086145855</v>
+        <v>350</v>
       </c>
       <c r="I29" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29654,16 +29654,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
-        <v>342.6720972219126</v>
+        <v>262.1624218828912</v>
       </c>
       <c r="F30" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>263.0617733495848</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H30" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>217.1263858913485</v>
@@ -29699,7 +29699,7 @@
         <v>350</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="U30" t="n">
         <v>350</v>
@@ -29778,7 +29778,7 @@
         <v>350</v>
       </c>
       <c r="T31" t="n">
-        <v>342.2113306341344</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U31" t="n">
         <v>350</v>
@@ -29809,7 +29809,7 @@
         <v>350</v>
       </c>
       <c r="D32" t="n">
-        <v>342.1538086145855</v>
+        <v>350</v>
       </c>
       <c r="E32" t="n">
         <v>350</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S32" t="n">
         <v>350</v>
@@ -29885,19 +29885,19 @@
         <v>350</v>
       </c>
       <c r="C33" t="n">
-        <v>350</v>
+        <v>285.2599243722601</v>
       </c>
       <c r="D33" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F33" t="n">
-        <v>252.6980156874615</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H33" t="n">
         <v>332.1680871864211</v>
@@ -30015,7 +30015,7 @@
         <v>350</v>
       </c>
       <c r="T34" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U34" t="n">
         <v>350</v>
@@ -30027,7 +30027,7 @@
         <v>350</v>
       </c>
       <c r="X34" t="n">
-        <v>342.2113306341344</v>
+        <v>350</v>
       </c>
       <c r="Y34" t="n">
         <v>350</v>
@@ -30091,7 +30091,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S35" t="n">
-        <v>342.1538086145855</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T35" t="n">
         <v>350</v>
@@ -30119,22 +30119,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="D36" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>255.7338705714973</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H36" t="n">
         <v>332.1680871864211</v>
@@ -30216,7 +30216,7 @@
         <v>350</v>
       </c>
       <c r="H37" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="I37" t="n">
         <v>350</v>
@@ -30258,7 +30258,7 @@
         <v>350</v>
       </c>
       <c r="V37" t="n">
-        <v>342.2113306341344</v>
+        <v>350</v>
       </c>
       <c r="W37" t="n">
         <v>350</v>
@@ -30298,7 +30298,7 @@
         <v>350</v>
       </c>
       <c r="I38" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>243.0324074428798</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S38" t="n">
         <v>350</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>276.9584798124342</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="D39" t="n">
         <v>347.9376868977026</v>
@@ -30368,7 +30368,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
         <v>325.7395358750273</v>
@@ -30435,7 +30435,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>342.2113306341345</v>
+        <v>350</v>
       </c>
       <c r="C40" t="n">
         <v>350</v>
@@ -30462,7 +30462,7 @@
         <v>350</v>
       </c>
       <c r="K40" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="L40" t="n">
         <v>350</v>
@@ -30535,7 +30535,7 @@
         <v>350</v>
       </c>
       <c r="I41" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>243.0324074428798</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S41" t="n">
         <v>350</v>
@@ -30641,10 +30641,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R42" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="T42" t="n">
         <v>350</v>
@@ -30653,7 +30653,7 @@
         <v>350</v>
       </c>
       <c r="V42" t="n">
-        <v>287.3222374745574</v>
+        <v>350</v>
       </c>
       <c r="W42" t="n">
         <v>350</v>
@@ -30662,7 +30662,7 @@
         <v>350</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="43">
@@ -30726,7 +30726,7 @@
         <v>350</v>
       </c>
       <c r="T43" t="n">
-        <v>342.2113306341344</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U43" t="n">
         <v>350</v>
@@ -30772,7 +30772,7 @@
         <v>350</v>
       </c>
       <c r="I44" t="n">
-        <v>142.2349682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30799,7 +30799,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S44" t="n">
         <v>350</v>
@@ -30836,7 +30836,7 @@
         <v>350</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E45" t="n">
         <v>342.6720972219126</v>
@@ -30878,7 +30878,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R45" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="S45" t="n">
         <v>350</v>
@@ -30890,7 +30890,7 @@
         <v>350</v>
       </c>
       <c r="V45" t="n">
-        <v>285.25992437226</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
         <v>350</v>
@@ -30933,7 +30933,7 @@
         <v>350</v>
       </c>
       <c r="J46" t="n">
-        <v>342.2113306341344</v>
+        <v>350</v>
       </c>
       <c r="K46" t="n">
         <v>350</v>
@@ -30978,7 +30978,7 @@
         <v>350</v>
       </c>
       <c r="Y46" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
     </row>
   </sheetData>
@@ -34743,7 +34743,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -34752,7 +34752,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>403.989898989899</v>
       </c>
       <c r="N2" t="n">
         <v>421</v>
@@ -34761,10 +34761,10 @@
         <v>421</v>
       </c>
       <c r="P2" t="n">
-        <v>8.728168648832536</v>
+        <v>421</v>
       </c>
       <c r="Q2" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34880,10 +34880,10 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
@@ -34892,19 +34892,19 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>154.95612715847</v>
+        <v>59.65711268880853</v>
       </c>
       <c r="H4" t="n">
-        <v>22.84746070643409</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,7 +34928,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T4" t="n">
         <v>189.9754334937423</v>
@@ -34940,7 +34940,7 @@
         <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
         <v>152.5563545698924</v>
@@ -34983,25 +34983,25 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>403.9898989898991</v>
       </c>
       <c r="M5" t="n">
         <v>421</v>
       </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>421</v>
-      </c>
-      <c r="O5" t="n">
-        <v>421</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>403.989898989899</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35114,7 +35114,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
         <v>127.2747533519553</v>
@@ -35123,25 +35123,25 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>154.95612715847</v>
+        <v>21.58525178687148</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35174,13 +35174,13 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
         <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>131.8593224151016</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
         <v>112.5346471505376</v>
@@ -35220,7 +35220,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>403.9898989898991</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -35238,7 +35238,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>403.989898989899</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35357,28 +35357,28 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
-        <v>22.24655620541628</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>111.479226198857</v>
+        <v>44.97700014532477</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35411,16 +35411,16 @@
         <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
         <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35454,10 +35454,10 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>138.3354305236338</v>
+        <v>20.40522350612654</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -35466,16 +35466,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="O11" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35642,7 +35642,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>132.1867641278766</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U13" t="n">
         <v>199.0416087255421</v>
@@ -35691,10 +35691,10 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -35703,16 +35703,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N14" t="n">
-        <v>560</v>
+        <v>300.1141042229716</v>
       </c>
       <c r="O14" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>21.36481946572209</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35879,7 +35879,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>132.1867641278766</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U16" t="n">
         <v>199.0416087255421</v>
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="L17" t="n">
-        <v>559.9999999999999</v>
+        <v>559</v>
       </c>
       <c r="M17" t="n">
-        <v>94.34434843164898</v>
+        <v>141.1524110730751</v>
       </c>
       <c r="N17" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -35949,7 +35949,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36116,13 +36116,13 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U19" t="n">
         <v>199.0416087255421</v>
       </c>
       <c r="V19" t="n">
-        <v>143.0410204179181</v>
+        <v>150.8296897837838</v>
       </c>
       <c r="W19" t="n">
         <v>123.6271901612903</v>
@@ -36165,10 +36165,10 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>20.40522350612657</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -36177,16 +36177,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P20" t="n">
-        <v>303.0737001825676</v>
+        <v>559</v>
       </c>
       <c r="Q20" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36353,7 +36353,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>132.1867641278766</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U22" t="n">
         <v>199.0416087255421</v>
@@ -36402,25 +36402,25 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>21.36481946572204</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>560</v>
+        <v>184.1434931650601</v>
       </c>
       <c r="M23" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P23" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -36551,7 +36551,7 @@
         <v>75.61714403225807</v>
       </c>
       <c r="G25" t="n">
-        <v>97.16745779260444</v>
+        <v>104.95612715847</v>
       </c>
       <c r="H25" t="n">
         <v>121.2288738983814</v>
@@ -36560,7 +36560,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J25" t="n">
-        <v>314.7310511640923</v>
+        <v>306.9423817982264</v>
       </c>
       <c r="K25" t="n">
         <v>61.47922619885696</v>
@@ -36639,25 +36639,25 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>395.2617303410664</v>
+        <v>136.375834564038</v>
       </c>
       <c r="K26" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>560.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>259.0826180905826</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q26" t="n">
         <v>443.0293889420883</v>
@@ -36827,7 +36827,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>132.1867641278766</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U28" t="n">
         <v>199.0416087255421</v>
@@ -36876,28 +36876,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>138.3354305236338</v>
+        <v>559</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M29" t="n">
-        <v>516.0089179080152</v>
+        <v>141.1524110730751</v>
       </c>
       <c r="N29" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P29" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37064,7 +37064,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>132.1867641278766</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U31" t="n">
         <v>199.0416087255421</v>
@@ -37113,25 +37113,25 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L32" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N32" t="n">
-        <v>94.34434843164887</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="O32" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>443.0293889420883</v>
@@ -37301,7 +37301,7 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U34" t="n">
         <v>199.0416087255421</v>
@@ -37313,7 +37313,7 @@
         <v>123.6271901612903</v>
       </c>
       <c r="X34" t="n">
-        <v>94.7676852040268</v>
+        <v>102.5563545698924</v>
       </c>
       <c r="Y34" t="n">
         <v>62.53464715053764</v>
@@ -37353,22 +37353,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K35" t="n">
-        <v>142.1120070326709</v>
+        <v>559</v>
       </c>
       <c r="L35" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N35" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="P35" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -37502,7 +37502,7 @@
         <v>104.95612715847</v>
       </c>
       <c r="H37" t="n">
-        <v>121.2288738983814</v>
+        <v>113.4402045325156</v>
       </c>
       <c r="I37" t="n">
         <v>173.3665443798817</v>
@@ -37544,7 +37544,7 @@
         <v>199.0416087255421</v>
       </c>
       <c r="V37" t="n">
-        <v>143.0410204179181</v>
+        <v>150.8296897837838</v>
       </c>
       <c r="W37" t="n">
         <v>123.6271901612903</v>
@@ -37593,16 +37593,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>259.0826180905825</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -37721,7 +37721,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>55.09753029705578</v>
+        <v>62.88619966292134</v>
       </c>
       <c r="C40" t="n">
         <v>77.27475335195533</v>
@@ -37748,7 +37748,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K40" t="n">
-        <v>61.47922619885696</v>
+        <v>53.69055683299113</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -37824,7 +37824,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -37836,13 +37836,13 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="O41" t="n">
-        <v>138.3354305236338</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P41" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>443.0293889420883</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>132.1867641278766</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U43" t="n">
         <v>199.0416087255421</v>
@@ -38061,28 +38061,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>559.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>21.36481946572209</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38219,7 +38219,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J46" t="n">
-        <v>306.9423817982266</v>
+        <v>314.7310511640923</v>
       </c>
       <c r="K46" t="n">
         <v>61.47922619885696</v>
@@ -38264,7 +38264,7 @@
         <v>102.5563545698924</v>
       </c>
       <c r="Y46" t="n">
-        <v>62.53464715053764</v>
+        <v>54.74597778467183</v>
       </c>
     </row>
   </sheetData>
